--- a/docentes/Faltante Faltante Faltante - Estadisticos 20241.xlsx
+++ b/docentes/Faltante Faltante Faltante - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="471">
   <si>
     <t>Mat</t>
   </si>
@@ -103,13 +103,124 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CUAPIO</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>BERULES</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
   </si>
   <si>
     <t>JUSTO</t>
@@ -121,49 +232,91 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>BUSTOS</t>
   </si>
   <si>
     <t>LARA</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>AZPIRI</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>VEGA</t>
   </si>
   <si>
     <t>ABREGO</t>
@@ -178,10 +331,7 @@
     <t>HERRERA</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>LARRACILLA</t>
   </si>
   <si>
     <t>MELO</t>
@@ -193,12 +343,6 @@
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
@@ -208,246 +352,150 @@
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>IBARRA</t>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BALCAZAR</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
   </si>
   <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>GUERRERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>QUIROGA</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
   </si>
   <si>
     <t>CALVA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ECHAVARRIA</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
     <t>SAAVEDRA</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>AMARO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>BERULES</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BALCAZAR</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>QUIROGA</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
     <t>BORBONIO</t>
   </si>
   <si>
@@ -466,9 +514,6 @@
     <t>MAY</t>
   </si>
   <si>
-    <t>MARIN</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
@@ -478,6 +523,51 @@
     <t>TENORIO</t>
   </si>
   <si>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>ZAYAS</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
@@ -487,15 +577,30 @@
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
   </si>
   <si>
     <t>CAMARILLO</t>
   </si>
   <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>ALDUCIN</t>
   </si>
   <si>
@@ -505,12 +610,24 @@
     <t>GUEVARA</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>MIXTECO</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>ESPINOZA</t>
   </si>
   <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>SOLIS</t>
   </si>
   <si>
@@ -532,111 +649,54 @@
     <t>CORREA</t>
   </si>
   <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>POOT</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
   </si>
   <si>
     <t>TINOCO</t>
   </si>
   <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>MIXTECO</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
@@ -649,9 +709,6 @@
     <t>DURAND</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>MIXCOA</t>
   </si>
   <si>
@@ -700,19 +757,160 @@
     <t>SALINAS</t>
   </si>
   <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>JOSUE YAHIR</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>ARMANDO GABRIEL</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>REGINA DAYTRI</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS PABLO</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MELANIE YARETZI</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>VANESA</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>PABLO AZAEL</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OSMAR EDUARDO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
     <t>ERICK ANGEL</t>
   </si>
   <si>
+    <t>VICENTE ABIMAEL</t>
+  </si>
+  <si>
+    <t>DANA INGRID</t>
+  </si>
+  <si>
     <t>OMAR DAVID</t>
   </si>
   <si>
-    <t>JUAN SEBASTIAN</t>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>DANILO</t>
   </si>
   <si>
     <t>JAQUELINE</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
@@ -721,57 +919,147 @@
     <t>JOEL MIGUEL</t>
   </si>
   <si>
-    <t>KEVYN DANIEL</t>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
   </si>
   <si>
     <t>XIMENA</t>
   </si>
   <si>
+    <t>ANGEL NAIN</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
     <t>JANETH</t>
   </si>
   <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
     <t>MARIAM MICHAELL</t>
   </si>
   <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
     <t>YAMILET</t>
   </si>
   <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
     <t>ALEX TADEO</t>
   </si>
   <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
     <t>ANGEL EDUC</t>
   </si>
   <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
+    <t>ARELI DANAE</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>ANIELA SAMANTA</t>
   </si>
   <si>
+    <t>CONCEPCION GUADALUPE</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>DAFNE</t>
+  </si>
+  <si>
+    <t>HEIDI</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>GUADALUPE ANAHI</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
     <t>RAMSES</t>
   </si>
   <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
     <t>MARIANA</t>
   </si>
   <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
     <t>ESTEFANIA</t>
   </si>
   <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>SAMIR</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
     <t>KARINA</t>
   </si>
   <si>
+    <t>MIREILLE</t>
+  </si>
+  <si>
     <t>SULU ALAN</t>
   </si>
   <si>
@@ -811,6 +1099,9 @@
     <t>KEIRA</t>
   </si>
   <si>
+    <t>MONICA</t>
+  </si>
+  <si>
     <t>URIEL</t>
   </si>
   <si>
@@ -838,445 +1129,307 @@
     <t>MARIEL</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>HUGO ANTONIO</t>
   </si>
   <si>
     <t>JUAN CARLOS</t>
   </si>
   <si>
-    <t>ARMANDO</t>
+    <t>JURISEL</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
   </si>
   <si>
     <t>JUSTIN GIOVANNI</t>
   </si>
   <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>YURI MONSERRAT</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
     <t>MARIA GUADALUPE</t>
   </si>
   <si>
-    <t>DENISSE</t>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>MAR EDITH</t>
+  </si>
+  <si>
+    <t>MELISA</t>
+  </si>
+  <si>
+    <t>JUAN ALONSO</t>
+  </si>
+  <si>
+    <t>CRIZULY AMITHAI</t>
+  </si>
+  <si>
+    <t>ADIEL ALONSO</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>EUNICE</t>
+  </si>
+  <si>
+    <t>REYNA IVETT</t>
+  </si>
+  <si>
+    <t>HANNA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>KAROL BALAAM</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>YASMIN</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
+  </si>
+  <si>
+    <t>ROSA EVELYN</t>
+  </si>
+  <si>
+    <t>VANIA</t>
+  </si>
+  <si>
+    <t>DARLA AMERICA</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>DIANA PAOLA</t>
+  </si>
+  <si>
+    <t>MARIEL BIDEMI</t>
+  </si>
+  <si>
+    <t>CARMEN VANELI</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
   </si>
   <si>
     <t>LORENA</t>
   </si>
   <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
     <t>DORIAN</t>
   </si>
   <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>VIANEY SAMARI</t>
+  </si>
+  <si>
+    <t>CLARA LIZBETH</t>
+  </si>
+  <si>
+    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>JULIO ALBERTO</t>
   </si>
   <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
+    <t>GIANCARLO</t>
+  </si>
+  <si>
+    <t>ANA ISABEL</t>
+  </si>
+  <si>
+    <t>NAIDELYN</t>
+  </si>
+  <si>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>JOANNA OCTAVIA</t>
   </si>
   <si>
     <t>JOSE ARTURO</t>
   </si>
   <si>
+    <t>ARELY SUSANA</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>YAEL ISSAI</t>
+  </si>
+  <si>
+    <t>IRMA GUADALUPE</t>
+  </si>
+  <si>
     <t>ANGEL DANIEL</t>
   </si>
   <si>
-    <t>AXEL</t>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>LEYLA SARAI</t>
+  </si>
+  <si>
+    <t>LUZ MARIA</t>
+  </si>
+  <si>
+    <t>NOELIA</t>
+  </si>
+  <si>
+    <t>ABRIL AMAYRANI</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
   </si>
   <si>
     <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>OSMAR EDUARDO</t>
-  </si>
-  <si>
-    <t>VICENTE ABIMAEL</t>
-  </si>
-  <si>
-    <t>DANA INGRID</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>FELIX</t>
-  </si>
-  <si>
-    <t>DANILO</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>GUADALUPE ANAHI</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>REGINA DAYTRI</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>MIREILLE</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ABRAHAN</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>YURI MONSERRAT</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>MAR EDITH</t>
-  </si>
-  <si>
-    <t>MELISA</t>
-  </si>
-  <si>
-    <t>JUAN ALONSO</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>ADIEL ALONSO</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>EUNICE</t>
-  </si>
-  <si>
-    <t>REYNA IVETT</t>
-  </si>
-  <si>
-    <t>HANNA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>ROSA EVELYN</t>
-  </si>
-  <si>
-    <t>VANIA</t>
-  </si>
-  <si>
-    <t>DARLA AMERICA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>DIANA PAOLA</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>CARMEN VANELI</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>ANGEL JESUS</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>VIANEY SAMARI</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
-  </si>
-  <si>
-    <t>ANA ISABEL</t>
-  </si>
-  <si>
-    <t>NAIDELYN</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JAZIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
-  </si>
-  <si>
-    <t>ARELY SUSANA</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>YAEL ISSAI</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>NOELIA</t>
-  </si>
-  <si>
-    <t>ABRIL AMAYRANI</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
   </si>
 </sst>
 </file>
@@ -2028,16 +2181,19 @@
         <v>40</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>40</v>
       </c>
-      <c r="E2">
-        <v>40</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2051,16 +2207,19 @@
         <v>24</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>24</v>
       </c>
-      <c r="E3">
-        <v>24</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2074,16 +2233,19 @@
         <v>36</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>36</v>
       </c>
-      <c r="E4">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2097,16 +2259,19 @@
         <v>28</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>28</v>
       </c>
-      <c r="E5">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2120,16 +2285,19 @@
         <v>35</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>35</v>
       </c>
-      <c r="E6">
-        <v>35</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2143,16 +2311,19 @@
         <v>24</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>24</v>
       </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2166,16 +2337,19 @@
         <v>37</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>37</v>
       </c>
-      <c r="E8">
-        <v>37</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2189,16 +2363,19 @@
         <v>21</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>21</v>
       </c>
-      <c r="E9">
-        <v>21</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2212,16 +2389,19 @@
         <v>25</v>
       </c>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>25</v>
       </c>
-      <c r="E10">
-        <v>25</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2235,16 +2415,19 @@
         <v>19</v>
       </c>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>19</v>
       </c>
-      <c r="E11">
-        <v>19</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2258,16 +2441,19 @@
         <v>21</v>
       </c>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>21</v>
       </c>
-      <c r="E12">
-        <v>21</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2281,16 +2467,19 @@
         <v>10</v>
       </c>
       <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>10</v>
       </c>
-      <c r="E13">
+      <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
         <v>10</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2346,16 +2535,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>97.5</v>
+        <v>85</v>
       </c>
       <c r="H2">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2618,7 +2807,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -2650,16 +2839,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920003</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -2673,16 +2862,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920005</v>
+        <v>23330051920008</v>
       </c>
       <c r="B3" t="s">
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2696,16 +2885,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920008</v>
+        <v>23330051920018</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -2719,16 +2908,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920014</v>
+        <v>23330051920023</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -2742,16 +2931,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920021</v>
+        <v>23330051920025</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -2765,22 +2954,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920020</v>
+        <v>23330051920192</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -2788,22 +2977,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920024</v>
+        <v>23330051920329</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -2811,16 +3000,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920192</v>
+        <v>23330051920324</v>
       </c>
       <c r="B9" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -2834,16 +3023,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920199</v>
+        <v>23330051920201</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -2857,16 +3046,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920201</v>
+        <v>22330051920196</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -2880,16 +3069,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920211</v>
+        <v>22330051920050</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -2903,16 +3092,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920079</v>
+        <v>23330051920251</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -2926,16 +3115,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920086</v>
+        <v>23330051920097</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -2949,16 +3138,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920088</v>
+        <v>23330051920111</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -2972,16 +3161,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920090</v>
+        <v>23330051920112</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -2995,22 +3184,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920234</v>
+        <v>23330051920222</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -3018,22 +3207,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920099</v>
+        <v>23330051920228</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -3041,22 +3230,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920104</v>
+        <v>23330051920231</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D19" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -3064,22 +3253,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920261</v>
+        <v>23330051920233</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -3087,22 +3276,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920221</v>
+        <v>23330051920285</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -3110,22 +3299,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920229</v>
+        <v>23330051920294</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -3133,22 +3322,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920245</v>
+        <v>23330051920295</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -3156,22 +3345,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920247</v>
+        <v>23330051920320</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -3179,22 +3368,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920267</v>
+        <v>23330051920357</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -3202,22 +3391,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920151</v>
+        <v>23330051920259</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -3225,22 +3414,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920152</v>
+        <v>23330051920065</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -3248,22 +3437,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920153</v>
+        <v>23330051920237</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -3271,22 +3460,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920155</v>
+        <v>23330051920278</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D29" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -3294,22 +3483,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920154</v>
+        <v>23330051920280</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G30">
         <v>2</v>
@@ -3317,22 +3506,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920325</v>
+        <v>23330051920319</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -3340,22 +3529,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920250</v>
+        <v>23330051920339</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="D32" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -3363,22 +3552,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920157</v>
+        <v>23330051920289</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -3386,22 +3575,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920158</v>
+        <v>23330051920303</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -3409,22 +3598,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920159</v>
+        <v>23330051920043</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -3432,22 +3621,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920161</v>
+        <v>23330051920144</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -3455,712 +3644,712 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920162</v>
+        <v>24330051920012</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D37" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920163</v>
+        <v>24330051920025</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920297</v>
+        <v>24330051920027</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920165</v>
+        <v>24330051920001</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920166</v>
+        <v>23330051920003</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D41" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920167</v>
+        <v>23330051920002</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920310</v>
+        <v>23330051920004</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="D43" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920169</v>
+        <v>23330051920005</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="D44" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920354</v>
+        <v>23330051920182</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920170</v>
+        <v>23330051920009</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920173</v>
+        <v>23330051920026</v>
       </c>
       <c r="B47" t="s">
         <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920172</v>
+        <v>23330051920010</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920311</v>
+        <v>23330051920012</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D49" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920174</v>
+        <v>23330051920013</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920295</v>
+        <v>23330051920014</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D51" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920308</v>
+        <v>23330051920204</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920083</v>
+        <v>23330051920321</v>
       </c>
       <c r="B53" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>23330051920065</v>
+        <v>23330051920021</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D54" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>23330051920215</v>
+        <v>23330051920020</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="D55" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>23330051920207</v>
+        <v>23330051920024</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>23330051920319</v>
+        <v>23330051920179</v>
       </c>
       <c r="B57" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="D57" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>23330051920339</v>
+        <v>23330051920180</v>
       </c>
       <c r="B58" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>23330051920289</v>
+        <v>23330051920190</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="D59" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>23330051920290</v>
+        <v>23330051920199</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>23330051920303</v>
+        <v>23330051920206</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>23330051920232</v>
+        <v>23330051920186</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C62" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>23330051920044</v>
+        <v>23330051920078</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C63" t="s">
         <v>43</v>
       </c>
       <c r="D63" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>23330051920118</v>
+        <v>23330051920077</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="D64" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>23330051920144</v>
+        <v>23330051920079</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="D65" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>23330051920150</v>
+        <v>23330051920080</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="D66" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>24330051920027</v>
+        <v>23330051920082</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D67" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -4168,22 +4357,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>23330051920002</v>
+        <v>23330051920085</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="D68" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -4191,22 +4380,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>23330051920004</v>
+        <v>23330051920086</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -4214,22 +4403,22 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>23330051920182</v>
+        <v>23330051920084</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -4237,22 +4426,22 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>23330051920009</v>
+        <v>23330051920087</v>
       </c>
       <c r="B71" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D71" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -4260,22 +4449,22 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>23330051920026</v>
+        <v>23330051920088</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C72" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="D72" t="s">
-        <v>231</v>
+        <v>313</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -4283,22 +4472,22 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>23330051920010</v>
+        <v>23330051920089</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="D73" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -4306,22 +4495,22 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>23330051920012</v>
+        <v>23330051920090</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="D74" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -4329,22 +4518,22 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>23330051920013</v>
+        <v>23330051920091</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C75" t="s">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="D75" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -4352,22 +4541,22 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>23330051920204</v>
+        <v>23330051920234</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D76" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -4375,22 +4564,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>23330051920321</v>
+        <v>23330051920094</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="D77" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -4398,22 +4587,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>23330051920179</v>
+        <v>23330051920099</v>
       </c>
       <c r="B78" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D78" t="s">
-        <v>162</v>
+        <v>319</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -4421,22 +4610,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>23330051920180</v>
+        <v>23330051920098</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -4444,22 +4633,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>23330051920190</v>
+        <v>23330051920100</v>
       </c>
       <c r="B80" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="D80" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -4467,22 +4656,22 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>23330051920206</v>
+        <v>23330051920102</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="D81" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -4490,22 +4679,22 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>23330051920186</v>
+        <v>23330051920103</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C82" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="D82" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
       </c>
       <c r="F82" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4513,16 +4702,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>23330051920078</v>
+        <v>23330051920104</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="D83" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -4536,16 +4725,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>23330051920077</v>
+        <v>23330051920261</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="C84" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="D84" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -4559,16 +4748,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>23330051920082</v>
+        <v>23330051920106</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C85" t="s">
         <v>181</v>
       </c>
       <c r="D85" t="s">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -4582,16 +4771,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>23330051920085</v>
+        <v>23330051920107</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C86" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="D86" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -4605,16 +4794,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>23330051920084</v>
+        <v>23330051920108</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="D87" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -4628,16 +4817,16 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>23330051920087</v>
+        <v>23330051920110</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C88" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -4651,16 +4840,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>23330051920089</v>
+        <v>23330051920114</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="D89" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -4674,16 +4863,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>23330051920091</v>
+        <v>23330051920115</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C90" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="D90" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -4697,22 +4886,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>23330051920094</v>
+        <v>23330051920218</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C91" t="s">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="D91" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -4720,22 +4909,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>23330051920098</v>
+        <v>23330051920221</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="D92" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -4743,22 +4932,22 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>23330051920100</v>
+        <v>23330051920223</v>
       </c>
       <c r="B93" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C93" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="D93" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
       </c>
       <c r="F93" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -4766,22 +4955,22 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>23330051920102</v>
+        <v>23330051920229</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="C94" t="s">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="D94" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
       </c>
       <c r="F94" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -4789,22 +4978,22 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>23330051920103</v>
+        <v>23330051920241</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -4812,22 +5001,22 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>23330051920106</v>
+        <v>23330051920335</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C96" t="s">
-        <v>175</v>
+        <v>53</v>
       </c>
       <c r="D96" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -4835,22 +5024,22 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>23330051920107</v>
+        <v>23330051920245</v>
       </c>
       <c r="B97" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="D97" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -4858,22 +5047,22 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>23330051920108</v>
+        <v>23330051920247</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D98" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -4881,22 +5070,22 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>23330051920111</v>
+        <v>23330051920249</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D99" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -4904,22 +5093,22 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>23330051920115</v>
+        <v>23330051920253</v>
       </c>
       <c r="B100" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C100" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="D100" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -4927,16 +5116,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>23330051920218</v>
+        <v>23330051920318</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="D101" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="E101" t="s">
         <v>9</v>
@@ -4950,16 +5139,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>23330051920228</v>
+        <v>23330051920258</v>
       </c>
       <c r="B102" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="D102" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
@@ -4973,16 +5162,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>23330051920335</v>
+        <v>23330051920264</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C103" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="D103" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
@@ -4996,16 +5185,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>23330051920318</v>
+        <v>23330051920265</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C104" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="D104" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -5019,16 +5208,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>23330051920258</v>
+        <v>23330051920267</v>
       </c>
       <c r="B105" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D105" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -5042,16 +5231,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>23330051920265</v>
+        <v>23330051920273</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="D106" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -5065,22 +5254,22 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107">
-        <v>23330051920273</v>
+        <v>23330051920151</v>
       </c>
       <c r="B107" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>42</v>
+        <v>203</v>
       </c>
       <c r="D107" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
       </c>
       <c r="F107" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -5088,22 +5277,22 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>23330051920281</v>
+        <v>23330051920152</v>
       </c>
       <c r="B108" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C108" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D108" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
       </c>
       <c r="F108" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -5111,22 +5300,22 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>23330051920283</v>
+        <v>23330051920153</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C109" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D109" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
       </c>
       <c r="F109" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -5134,22 +5323,22 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>23330051920284</v>
+        <v>23330051920155</v>
       </c>
       <c r="B110" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D110" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
       </c>
       <c r="F110" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -5157,22 +5346,22 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>23330051920292</v>
+        <v>23330051920154</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C111" t="s">
-        <v>88</v>
+        <v>205</v>
       </c>
       <c r="D111" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
       </c>
       <c r="F111" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -5180,22 +5369,22 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>23330051920365</v>
+        <v>23330051920325</v>
       </c>
       <c r="B112" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C112" t="s">
-        <v>54</v>
+        <v>206</v>
       </c>
       <c r="D112" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -5203,22 +5392,22 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>23330051920296</v>
+        <v>23330051920250</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="C113" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="D113" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
       </c>
       <c r="F113" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -5226,22 +5415,22 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>23330051920299</v>
+        <v>23330051920157</v>
       </c>
       <c r="B114" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C114" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="D114" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
       </c>
       <c r="F114" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -5249,22 +5438,22 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>23330051920348</v>
+        <v>23330051920158</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C115" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D115" t="s">
-        <v>235</v>
+        <v>355</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
       </c>
       <c r="F115" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -5272,22 +5461,22 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>23330051920363</v>
+        <v>23330051920159</v>
       </c>
       <c r="B116" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C116" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D116" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
       </c>
       <c r="F116" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -5295,22 +5484,22 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>23330051920326</v>
+        <v>23330051920161</v>
       </c>
       <c r="B117" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C117" t="s">
-        <v>66</v>
+        <v>207</v>
       </c>
       <c r="D117" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
       </c>
       <c r="F117" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -5318,22 +5507,22 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>23330051920048</v>
+        <v>23330051920162</v>
       </c>
       <c r="B118" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C118" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="D118" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="E118" t="s">
         <v>9</v>
       </c>
       <c r="F118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -5341,22 +5530,22 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>23330051920049</v>
+        <v>23330051920163</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="C119" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="D119" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="E119" t="s">
         <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -5364,22 +5553,22 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>23330051920050</v>
+        <v>23330051920164</v>
       </c>
       <c r="B120" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C120" t="s">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="D120" t="s">
-        <v>283</v>
+        <v>360</v>
       </c>
       <c r="E120" t="s">
         <v>9</v>
       </c>
       <c r="F120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -5387,22 +5576,22 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>23330051920053</v>
+        <v>23330051920297</v>
       </c>
       <c r="B121" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C121" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="D121" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="E121" t="s">
         <v>9</v>
       </c>
       <c r="F121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -5410,22 +5599,22 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>23330051920227</v>
+        <v>23330051920165</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="C122" t="s">
-        <v>191</v>
+        <v>33</v>
       </c>
       <c r="D122" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="E122" t="s">
         <v>9</v>
       </c>
       <c r="F122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -5433,22 +5622,22 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>23330051920054</v>
+        <v>23330051920166</v>
       </c>
       <c r="B123" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C123" t="s">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="D123" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="E123" t="s">
         <v>9</v>
       </c>
       <c r="F123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -5456,22 +5645,22 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>23330051920055</v>
+        <v>23330051920167</v>
       </c>
       <c r="B124" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C124" t="s">
-        <v>192</v>
+        <v>57</v>
       </c>
       <c r="D124" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
       </c>
       <c r="F124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -5479,22 +5668,22 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>23330051920056</v>
+        <v>23330051920310</v>
       </c>
       <c r="B125" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="C125" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D125" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
       </c>
       <c r="F125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -5502,22 +5691,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>23330051920057</v>
+        <v>23330051920169</v>
       </c>
       <c r="B126" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C126" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D126" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
       </c>
       <c r="F126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -5525,22 +5714,22 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>23330051920058</v>
+        <v>23330051920354</v>
       </c>
       <c r="B127" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C127" t="s">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="D127" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="E127" t="s">
         <v>9</v>
       </c>
       <c r="F127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -5548,22 +5737,22 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>23330051920246</v>
+        <v>23330051920170</v>
       </c>
       <c r="B128" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="C128" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D128" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
       </c>
       <c r="F128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -5571,22 +5760,22 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>23330051920060</v>
+        <v>23330051920173</v>
       </c>
       <c r="B129" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="C129" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="E129" t="s">
         <v>9</v>
       </c>
       <c r="F129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -5594,22 +5783,22 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>23330051920061</v>
+        <v>23330051920172</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C130" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="D130" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E130" t="s">
         <v>9</v>
       </c>
       <c r="F130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -5617,22 +5806,22 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>23330051920062</v>
+        <v>23330051920311</v>
       </c>
       <c r="B131" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C131" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D131" t="s">
-        <v>244</v>
+        <v>370</v>
       </c>
       <c r="E131" t="s">
         <v>9</v>
       </c>
       <c r="F131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -5640,22 +5829,22 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>23330051920307</v>
+        <v>23330051920174</v>
       </c>
       <c r="B132" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="C132" t="s">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="D132" t="s">
-        <v>257</v>
+        <v>371</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
       </c>
       <c r="F132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -5663,22 +5852,22 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>23330051920063</v>
+        <v>23330051920281</v>
       </c>
       <c r="B133" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="C133" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="D133" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
       </c>
       <c r="F133" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5686,22 +5875,22 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>23330051920064</v>
+        <v>23330051920283</v>
       </c>
       <c r="B134" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C134" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="D134" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
       </c>
       <c r="F134" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -5709,22 +5898,22 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>23330051920260</v>
+        <v>23330051920284</v>
       </c>
       <c r="B135" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C135" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D135" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
       </c>
       <c r="F135" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -5732,22 +5921,22 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>23330051920066</v>
+        <v>23330051920292</v>
       </c>
       <c r="B136" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C136" t="s">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="D136" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="E136" t="s">
         <v>9</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -5755,22 +5944,22 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>23330051920067</v>
+        <v>23330051920365</v>
       </c>
       <c r="B137" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C137" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="D137" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
       </c>
       <c r="F137" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -5778,22 +5967,22 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>23330051920068</v>
+        <v>23330051920296</v>
       </c>
       <c r="B138" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C138" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="D138" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
       </c>
       <c r="F138" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -5801,22 +5990,22 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>23330051920069</v>
+        <v>23330051920299</v>
       </c>
       <c r="B139" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C139" t="s">
-        <v>198</v>
+        <v>83</v>
       </c>
       <c r="D139" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
       </c>
       <c r="F139" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -5824,22 +6013,22 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>23330051920070</v>
+        <v>23330051920308</v>
       </c>
       <c r="B140" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C140" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="D140" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
       </c>
       <c r="F140" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -5847,22 +6036,22 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>23330051920330</v>
+        <v>23330051920348</v>
       </c>
       <c r="B141" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C141" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D141" t="s">
-        <v>358</v>
+        <v>302</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
       </c>
       <c r="F141" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -5870,22 +6059,22 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>23330051920272</v>
+        <v>23330051920363</v>
       </c>
       <c r="B142" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="D142" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
       </c>
       <c r="F142" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -5893,22 +6082,22 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
-        <v>23330051920073</v>
+        <v>23330051920326</v>
       </c>
       <c r="B143" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="C143" t="s">
-        <v>199</v>
+        <v>49</v>
       </c>
       <c r="D143" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
       </c>
       <c r="F143" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -5916,16 +6105,16 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>23330051920074</v>
+        <v>23330051920048</v>
       </c>
       <c r="B144" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C144" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="D144" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
@@ -5939,16 +6128,16 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>23330051920075</v>
+        <v>23330051920049</v>
       </c>
       <c r="B145" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C145" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="D145" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
@@ -5962,22 +6151,22 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>23330051920213</v>
+        <v>23330051920050</v>
       </c>
       <c r="B146" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C146" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D146" t="s">
-        <v>363</v>
+        <v>276</v>
       </c>
       <c r="E146" t="s">
         <v>9</v>
       </c>
       <c r="F146" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G146">
         <v>1</v>
@@ -5985,22 +6174,22 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>23330051920226</v>
+        <v>23330051920083</v>
       </c>
       <c r="B147" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C147" t="s">
-        <v>202</v>
+        <v>28</v>
       </c>
       <c r="D147" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="E147" t="s">
         <v>9</v>
       </c>
       <c r="F147" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -6008,22 +6197,22 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>23330051920216</v>
+        <v>23330051920053</v>
       </c>
       <c r="B148" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="C148" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="D148" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="E148" t="s">
         <v>9</v>
       </c>
       <c r="F148" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -6031,22 +6220,22 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>23330051920240</v>
+        <v>23330051920227</v>
       </c>
       <c r="B149" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="C149" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="D149" t="s">
-        <v>282</v>
+        <v>385</v>
       </c>
       <c r="E149" t="s">
         <v>9</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -6054,22 +6243,22 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
-        <v>23330051920244</v>
+        <v>23330051920054</v>
       </c>
       <c r="B150" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C150" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D150" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="E150" t="s">
         <v>9</v>
       </c>
       <c r="F150" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -6077,22 +6266,22 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>23330051920333</v>
+        <v>23330051920055</v>
       </c>
       <c r="B151" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C151" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D151" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
       </c>
       <c r="F151" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -6100,22 +6289,22 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152">
-        <v>23330051920252</v>
+        <v>23330051920056</v>
       </c>
       <c r="B152" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="C152" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D152" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
       </c>
       <c r="F152" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -6123,22 +6312,22 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>23330051920239</v>
+        <v>23330051920057</v>
       </c>
       <c r="B153" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C153" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D153" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
       </c>
       <c r="F153" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -6146,22 +6335,22 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>23330051920328</v>
+        <v>23330051920058</v>
       </c>
       <c r="B154" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="C154" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="D154" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -6169,22 +6358,22 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>23330051920256</v>
+        <v>23330051920246</v>
       </c>
       <c r="B155" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C155" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D155" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
       </c>
       <c r="F155" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -6192,22 +6381,22 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>23330051920257</v>
+        <v>23330051920060</v>
       </c>
       <c r="B156" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C156" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="D156" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -6215,22 +6404,22 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>23330051920270</v>
+        <v>23330051920061</v>
       </c>
       <c r="B157" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C157" t="s">
-        <v>42</v>
+        <v>216</v>
       </c>
       <c r="D157" t="s">
-        <v>244</v>
+        <v>393</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
       </c>
       <c r="F157" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -6238,22 +6427,22 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>23330051920276</v>
+        <v>23330051920062</v>
       </c>
       <c r="B158" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="C158" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D158" t="s">
-        <v>373</v>
+        <v>324</v>
       </c>
       <c r="E158" t="s">
         <v>9</v>
       </c>
       <c r="F158" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -6261,22 +6450,22 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>23330051920277</v>
+        <v>23330051920307</v>
       </c>
       <c r="B159" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="C159" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="D159" t="s">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="E159" t="s">
         <v>9</v>
       </c>
       <c r="F159" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G159">
         <v>1</v>
@@ -6284,22 +6473,22 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>23330051920279</v>
+        <v>23330051920063</v>
       </c>
       <c r="B160" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="C160" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="D160" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="E160" t="s">
         <v>9</v>
       </c>
       <c r="F160" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -6307,22 +6496,22 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>23330051920287</v>
+        <v>23330051920064</v>
       </c>
       <c r="B161" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="C161" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D161" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E161" t="s">
         <v>9</v>
       </c>
       <c r="F161" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -6330,22 +6519,22 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>23330051920288</v>
+        <v>23330051920260</v>
       </c>
       <c r="B162" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C162" t="s">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="D162" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E162" t="s">
         <v>9</v>
       </c>
       <c r="F162" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -6353,22 +6542,22 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>23330051920300</v>
+        <v>23330051920066</v>
       </c>
       <c r="B163" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="C163" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D163" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="E163" t="s">
         <v>9</v>
       </c>
       <c r="F163" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -6376,22 +6565,22 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>23330051920302</v>
+        <v>23330051920067</v>
       </c>
       <c r="B164" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="C164" t="s">
-        <v>141</v>
+        <v>219</v>
       </c>
       <c r="D164" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="E164" t="s">
         <v>9</v>
       </c>
       <c r="F164" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -6399,22 +6588,22 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>23330051920304</v>
+        <v>23330051920068</v>
       </c>
       <c r="B165" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C165" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="D165" t="s">
-        <v>307</v>
+        <v>399</v>
       </c>
       <c r="E165" t="s">
         <v>9</v>
       </c>
       <c r="F165" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -6422,22 +6611,22 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <v>23330051920029</v>
+        <v>23330051920069</v>
       </c>
       <c r="B166" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C166" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="D166" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
       </c>
       <c r="F166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -6445,22 +6634,22 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167">
-        <v>23330051920031</v>
+        <v>23330051920070</v>
       </c>
       <c r="B167" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="C167" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="D167" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="E167" t="s">
         <v>9</v>
       </c>
       <c r="F167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -6468,22 +6657,22 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168">
-        <v>23330051920030</v>
+        <v>23330051920330</v>
       </c>
       <c r="B168" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="C168" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="D168" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="E168" t="s">
         <v>9</v>
       </c>
       <c r="F168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -6491,22 +6680,22 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>22330051920007</v>
+        <v>23330051920272</v>
       </c>
       <c r="B169" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="C169" t="s">
-        <v>35</v>
+        <v>183</v>
       </c>
       <c r="D169" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="E169" t="s">
         <v>9</v>
       </c>
       <c r="F169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -6514,22 +6703,22 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170">
-        <v>23330051920033</v>
+        <v>23330051920073</v>
       </c>
       <c r="B170" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C170" t="s">
-        <v>209</v>
+        <v>31</v>
       </c>
       <c r="D170" t="s">
-        <v>334</v>
+        <v>404</v>
       </c>
       <c r="E170" t="s">
         <v>9</v>
       </c>
       <c r="F170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -6537,22 +6726,22 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>23330051920034</v>
+        <v>23330051920074</v>
       </c>
       <c r="B171" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="C171" t="s">
-        <v>42</v>
+        <v>174</v>
       </c>
       <c r="D171" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="E171" t="s">
         <v>9</v>
       </c>
       <c r="F171" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -6560,22 +6749,22 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>23330051920035</v>
+        <v>23330051920075</v>
       </c>
       <c r="B172" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="C172" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="D172" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="E172" t="s">
         <v>9</v>
       </c>
       <c r="F172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -6583,22 +6772,22 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>23330051920032</v>
+        <v>23330051920213</v>
       </c>
       <c r="B173" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C173" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D173" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="E173" t="s">
         <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -6606,22 +6795,22 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>23330051920039</v>
+        <v>23330051920226</v>
       </c>
       <c r="B174" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="C174" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D174" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="E174" t="s">
         <v>9</v>
       </c>
       <c r="F174" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -6629,22 +6818,22 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175">
-        <v>23330051920040</v>
+        <v>23330051920215</v>
       </c>
       <c r="B175" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C175" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="D175" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="E175" t="s">
         <v>9</v>
       </c>
       <c r="F175" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -6652,22 +6841,22 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176">
-        <v>23330051920041</v>
+        <v>23330051920216</v>
       </c>
       <c r="B176" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="C176" t="s">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="D176" t="s">
-        <v>232</v>
+        <v>410</v>
       </c>
       <c r="E176" t="s">
         <v>9</v>
       </c>
       <c r="F176" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -6675,22 +6864,22 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>23330051920042</v>
+        <v>23330051920240</v>
       </c>
       <c r="B177" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C177" t="s">
-        <v>40</v>
+        <v>132</v>
       </c>
       <c r="D177" t="s">
-        <v>387</v>
+        <v>275</v>
       </c>
       <c r="E177" t="s">
         <v>9</v>
       </c>
       <c r="F177" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G177">
         <v>1</v>
@@ -6698,22 +6887,22 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>23330051920209</v>
+        <v>23330051920244</v>
       </c>
       <c r="B178" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="D178" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="E178" t="s">
         <v>9</v>
       </c>
       <c r="F178" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -6721,22 +6910,22 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>23330051920210</v>
+        <v>23330051920333</v>
       </c>
       <c r="B179" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C179" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="D179" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="E179" t="s">
         <v>9</v>
       </c>
       <c r="F179" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -6744,22 +6933,22 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>23330051920046</v>
+        <v>23330051920252</v>
       </c>
       <c r="B180" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C180" t="s">
-        <v>214</v>
+        <v>47</v>
       </c>
       <c r="D180" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="E180" t="s">
         <v>9</v>
       </c>
       <c r="F180" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G180">
         <v>1</v>
@@ -6767,22 +6956,22 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>23330051920117</v>
+        <v>23330051920239</v>
       </c>
       <c r="B181" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C181" t="s">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="D181" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="E181" t="s">
         <v>9</v>
       </c>
       <c r="F181" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G181">
         <v>1</v>
@@ -6790,22 +6979,22 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>23330061460223</v>
+        <v>23330051920328</v>
       </c>
       <c r="B182" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="C182" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="D182" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="E182" t="s">
         <v>9</v>
       </c>
       <c r="F182" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G182">
         <v>1</v>
@@ -6813,22 +7002,22 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>23330051920119</v>
+        <v>23330051920256</v>
       </c>
       <c r="B183" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="C183" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D183" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="E183" t="s">
         <v>9</v>
       </c>
       <c r="F183" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G183">
         <v>1</v>
@@ -6836,22 +7025,22 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>23330051920120</v>
+        <v>23330051920257</v>
       </c>
       <c r="B184" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="C184" t="s">
-        <v>126</v>
+        <v>224</v>
       </c>
       <c r="D184" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="E184" t="s">
         <v>9</v>
       </c>
       <c r="F184" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -6859,22 +7048,22 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185">
-        <v>23330051920121</v>
+        <v>23330051920207</v>
       </c>
       <c r="B185" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C185" t="s">
-        <v>217</v>
+        <v>33</v>
       </c>
       <c r="D185" t="s">
-        <v>283</v>
+        <v>418</v>
       </c>
       <c r="E185" t="s">
         <v>9</v>
       </c>
       <c r="F185" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -6882,22 +7071,22 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>23330051920124</v>
+        <v>23330051920270</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="C186" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="D186" t="s">
-        <v>395</v>
+        <v>324</v>
       </c>
       <c r="E186" t="s">
         <v>9</v>
       </c>
       <c r="F186" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -6905,22 +7094,22 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>23330051920125</v>
+        <v>23330051920276</v>
       </c>
       <c r="B187" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C187" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D187" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="E187" t="s">
         <v>9</v>
       </c>
       <c r="F187" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -6928,22 +7117,22 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>23330051920126</v>
+        <v>23330051920277</v>
       </c>
       <c r="B188" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="C188" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="D188" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="E188" t="s">
         <v>9</v>
       </c>
       <c r="F188" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -6951,22 +7140,22 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>23330051920127</v>
+        <v>23330051920279</v>
       </c>
       <c r="B189" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="C189" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
       <c r="D189" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="E189" t="s">
         <v>9</v>
       </c>
       <c r="F189" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -6974,22 +7163,22 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>23330051920128</v>
+        <v>23330051920287</v>
       </c>
       <c r="B190" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="C190" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="D190" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="E190" t="s">
         <v>9</v>
       </c>
       <c r="F190" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -6997,22 +7186,22 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>23330051920129</v>
+        <v>23330051920288</v>
       </c>
       <c r="B191" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="C191" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D191" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="E191" t="s">
         <v>9</v>
       </c>
       <c r="F191" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -7020,22 +7209,22 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>23330051920130</v>
+        <v>23330051920290</v>
       </c>
       <c r="B192" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C192" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D192" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="E192" t="s">
         <v>9</v>
       </c>
       <c r="F192" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G192">
         <v>1</v>
@@ -7043,22 +7232,22 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193">
-        <v>23330051920133</v>
+        <v>23330051920300</v>
       </c>
       <c r="B193" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="C193" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="D193" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="E193" t="s">
         <v>9</v>
       </c>
       <c r="F193" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -7066,22 +7255,22 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>23330051920134</v>
+        <v>23330051920302</v>
       </c>
       <c r="B194" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C194" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="D194" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="E194" t="s">
         <v>9</v>
       </c>
       <c r="F194" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -7089,22 +7278,22 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>23330051920135</v>
+        <v>23330051920304</v>
       </c>
       <c r="B195" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="C195" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="D195" t="s">
-        <v>404</v>
+        <v>306</v>
       </c>
       <c r="E195" t="s">
         <v>9</v>
       </c>
       <c r="F195" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -7112,22 +7301,22 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>23330051920137</v>
+        <v>23330051920029</v>
       </c>
       <c r="B196" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C196" t="s">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="D196" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="E196" t="s">
         <v>9</v>
       </c>
       <c r="F196" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -7135,22 +7324,22 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>23330051920122</v>
+        <v>23330051920031</v>
       </c>
       <c r="B197" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C197" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="D197" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="E197" t="s">
         <v>9</v>
       </c>
       <c r="F197" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -7158,22 +7347,22 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>23330051920140</v>
+        <v>23330051920030</v>
       </c>
       <c r="B198" t="s">
         <v>148</v>
       </c>
       <c r="C198" t="s">
-        <v>47</v>
+        <v>228</v>
       </c>
       <c r="D198" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="E198" t="s">
         <v>9</v>
       </c>
       <c r="F198" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -7181,22 +7370,22 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>23330051920139</v>
+        <v>22330051920007</v>
       </c>
       <c r="B199" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="C199" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D199" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E199" t="s">
         <v>9</v>
       </c>
       <c r="F199" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G199">
         <v>1</v>
@@ -7204,22 +7393,22 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>23330051920138</v>
+        <v>23330051920033</v>
       </c>
       <c r="B200" t="s">
         <v>149</v>
       </c>
       <c r="C200" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D200" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="E200" t="s">
         <v>9</v>
       </c>
       <c r="F200" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G200">
         <v>1</v>
@@ -7227,22 +7416,22 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>23330051920255</v>
+        <v>23330051920034</v>
       </c>
       <c r="B201" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C201" t="s">
-        <v>222</v>
+        <v>43</v>
       </c>
       <c r="D201" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
       </c>
       <c r="F201" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G201">
         <v>1</v>
@@ -7250,22 +7439,22 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202">
-        <v>23330051920141</v>
+        <v>23330051920232</v>
       </c>
       <c r="B202" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="C202" t="s">
-        <v>223</v>
+        <v>50</v>
       </c>
       <c r="D202" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="E202" t="s">
         <v>9</v>
       </c>
       <c r="F202" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -7273,22 +7462,22 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203">
-        <v>23330051920315</v>
+        <v>23330051920035</v>
       </c>
       <c r="B203" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="C203" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
       <c r="D203" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="E203" t="s">
         <v>9</v>
       </c>
       <c r="F203" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -7296,22 +7485,22 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204">
-        <v>23330051920142</v>
+        <v>23330051920032</v>
       </c>
       <c r="B204" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="C204" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D204" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
       </c>
       <c r="F204" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -7319,22 +7508,22 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205">
-        <v>23330051920143</v>
+        <v>23330051920039</v>
       </c>
       <c r="B205" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="C205" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="D205" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
       </c>
       <c r="F205" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -7342,22 +7531,22 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206">
-        <v>23330051920146</v>
+        <v>23330051920040</v>
       </c>
       <c r="B206" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="C206" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="D206" t="s">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="E206" t="s">
         <v>9</v>
       </c>
       <c r="F206" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -7365,22 +7554,22 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207">
-        <v>23330051920147</v>
+        <v>23330051920041</v>
       </c>
       <c r="B207" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="C207" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D207" t="s">
-        <v>416</v>
+        <v>298</v>
       </c>
       <c r="E207" t="s">
         <v>9</v>
       </c>
       <c r="F207" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -7388,22 +7577,22 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208">
-        <v>23330051920346</v>
+        <v>23330051920042</v>
       </c>
       <c r="B208" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C208" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="D208" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="E208" t="s">
         <v>9</v>
       </c>
       <c r="F208" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -7411,22 +7600,22 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209">
-        <v>23330051920148</v>
+        <v>23330051920044</v>
       </c>
       <c r="B209" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C209" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="D209" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="E209" t="s">
         <v>9</v>
       </c>
       <c r="F209" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -7434,24 +7623,829 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210">
+        <v>23330051920209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>153</v>
+      </c>
+      <c r="C210" t="s">
+        <v>232</v>
+      </c>
+      <c r="D210" t="s">
+        <v>437</v>
+      </c>
+      <c r="E210" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" t="s">
+        <v>15</v>
+      </c>
+      <c r="G210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211">
+        <v>23330051920210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>154</v>
+      </c>
+      <c r="C211" t="s">
+        <v>154</v>
+      </c>
+      <c r="D211" t="s">
+        <v>438</v>
+      </c>
+      <c r="E211" t="s">
+        <v>9</v>
+      </c>
+      <c r="F211" t="s">
+        <v>15</v>
+      </c>
+      <c r="G211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212">
+        <v>23330051920046</v>
+      </c>
+      <c r="B212" t="s">
+        <v>155</v>
+      </c>
+      <c r="C212" t="s">
+        <v>233</v>
+      </c>
+      <c r="D212" t="s">
+        <v>439</v>
+      </c>
+      <c r="E212" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" t="s">
+        <v>15</v>
+      </c>
+      <c r="G212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213">
+        <v>23330051920116</v>
+      </c>
+      <c r="B213" t="s">
+        <v>156</v>
+      </c>
+      <c r="C213" t="s">
+        <v>60</v>
+      </c>
+      <c r="D213" t="s">
+        <v>438</v>
+      </c>
+      <c r="E213" t="s">
+        <v>9</v>
+      </c>
+      <c r="F213" t="s">
+        <v>16</v>
+      </c>
+      <c r="G213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214">
+        <v>23330051920117</v>
+      </c>
+      <c r="B214" t="s">
+        <v>157</v>
+      </c>
+      <c r="C214" t="s">
+        <v>234</v>
+      </c>
+      <c r="D214" t="s">
+        <v>440</v>
+      </c>
+      <c r="E214" t="s">
+        <v>9</v>
+      </c>
+      <c r="F214" t="s">
+        <v>16</v>
+      </c>
+      <c r="G214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215">
+        <v>23330051920118</v>
+      </c>
+      <c r="B215" t="s">
+        <v>158</v>
+      </c>
+      <c r="C215" t="s">
+        <v>57</v>
+      </c>
+      <c r="D215" t="s">
+        <v>441</v>
+      </c>
+      <c r="E215" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" t="s">
+        <v>16</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216">
+        <v>23330061460223</v>
+      </c>
+      <c r="B216" t="s">
+        <v>159</v>
+      </c>
+      <c r="C216" t="s">
+        <v>31</v>
+      </c>
+      <c r="D216" t="s">
+        <v>442</v>
+      </c>
+      <c r="E216" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" t="s">
+        <v>16</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217">
+        <v>23330051920119</v>
+      </c>
+      <c r="B217" t="s">
+        <v>160</v>
+      </c>
+      <c r="C217" t="s">
+        <v>235</v>
+      </c>
+      <c r="D217" t="s">
+        <v>443</v>
+      </c>
+      <c r="E217" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" t="s">
+        <v>16</v>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218">
+        <v>23330051920120</v>
+      </c>
+      <c r="B218" t="s">
+        <v>65</v>
+      </c>
+      <c r="C218" t="s">
+        <v>139</v>
+      </c>
+      <c r="D218" t="s">
+        <v>444</v>
+      </c>
+      <c r="E218" t="s">
+        <v>9</v>
+      </c>
+      <c r="F218" t="s">
+        <v>16</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219">
+        <v>23330051920121</v>
+      </c>
+      <c r="B219" t="s">
+        <v>161</v>
+      </c>
+      <c r="C219" t="s">
+        <v>236</v>
+      </c>
+      <c r="D219" t="s">
+        <v>276</v>
+      </c>
+      <c r="E219" t="s">
+        <v>9</v>
+      </c>
+      <c r="F219" t="s">
+        <v>16</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220">
+        <v>23330051920124</v>
+      </c>
+      <c r="B220" t="s">
+        <v>45</v>
+      </c>
+      <c r="C220" t="s">
+        <v>237</v>
+      </c>
+      <c r="D220" t="s">
+        <v>445</v>
+      </c>
+      <c r="E220" t="s">
+        <v>9</v>
+      </c>
+      <c r="F220" t="s">
+        <v>16</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221">
+        <v>23330051920125</v>
+      </c>
+      <c r="B221" t="s">
+        <v>33</v>
+      </c>
+      <c r="C221" t="s">
+        <v>94</v>
+      </c>
+      <c r="D221" t="s">
+        <v>446</v>
+      </c>
+      <c r="E221" t="s">
+        <v>9</v>
+      </c>
+      <c r="F221" t="s">
+        <v>16</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222">
+        <v>23330051920126</v>
+      </c>
+      <c r="B222" t="s">
+        <v>162</v>
+      </c>
+      <c r="C222" t="s">
+        <v>70</v>
+      </c>
+      <c r="D222" t="s">
+        <v>447</v>
+      </c>
+      <c r="E222" t="s">
+        <v>9</v>
+      </c>
+      <c r="F222" t="s">
+        <v>16</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223">
+        <v>23330051920127</v>
+      </c>
+      <c r="B223" t="s">
+        <v>43</v>
+      </c>
+      <c r="C223" t="s">
+        <v>206</v>
+      </c>
+      <c r="D223" t="s">
+        <v>448</v>
+      </c>
+      <c r="E223" t="s">
+        <v>9</v>
+      </c>
+      <c r="F223" t="s">
+        <v>16</v>
+      </c>
+      <c r="G223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224">
+        <v>23330051920128</v>
+      </c>
+      <c r="B224" t="s">
+        <v>43</v>
+      </c>
+      <c r="C224" t="s">
+        <v>139</v>
+      </c>
+      <c r="D224" t="s">
+        <v>449</v>
+      </c>
+      <c r="E224" t="s">
+        <v>9</v>
+      </c>
+      <c r="F224" t="s">
+        <v>16</v>
+      </c>
+      <c r="G224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225">
+        <v>23330051920129</v>
+      </c>
+      <c r="B225" t="s">
+        <v>43</v>
+      </c>
+      <c r="C225" t="s">
+        <v>48</v>
+      </c>
+      <c r="D225" t="s">
+        <v>450</v>
+      </c>
+      <c r="E225" t="s">
+        <v>9</v>
+      </c>
+      <c r="F225" t="s">
+        <v>16</v>
+      </c>
+      <c r="G225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226">
+        <v>23330051920130</v>
+      </c>
+      <c r="B226" t="s">
+        <v>43</v>
+      </c>
+      <c r="C226" t="s">
+        <v>238</v>
+      </c>
+      <c r="D226" t="s">
+        <v>451</v>
+      </c>
+      <c r="E226" t="s">
+        <v>9</v>
+      </c>
+      <c r="F226" t="s">
+        <v>16</v>
+      </c>
+      <c r="G226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227">
+        <v>23330051920133</v>
+      </c>
+      <c r="B227" t="s">
+        <v>125</v>
+      </c>
+      <c r="C227" t="s">
+        <v>129</v>
+      </c>
+      <c r="D227" t="s">
+        <v>452</v>
+      </c>
+      <c r="E227" t="s">
+        <v>9</v>
+      </c>
+      <c r="F227" t="s">
+        <v>16</v>
+      </c>
+      <c r="G227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228">
+        <v>23330051920134</v>
+      </c>
+      <c r="B228" t="s">
+        <v>83</v>
+      </c>
+      <c r="C228" t="s">
+        <v>43</v>
+      </c>
+      <c r="D228" t="s">
+        <v>453</v>
+      </c>
+      <c r="E228" t="s">
+        <v>9</v>
+      </c>
+      <c r="F228" t="s">
+        <v>16</v>
+      </c>
+      <c r="G228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229">
+        <v>23330051920135</v>
+      </c>
+      <c r="B229" t="s">
+        <v>83</v>
+      </c>
+      <c r="C229" t="s">
+        <v>186</v>
+      </c>
+      <c r="D229" t="s">
+        <v>454</v>
+      </c>
+      <c r="E229" t="s">
+        <v>9</v>
+      </c>
+      <c r="F229" t="s">
+        <v>16</v>
+      </c>
+      <c r="G229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230">
+        <v>23330051920137</v>
+      </c>
+      <c r="B230" t="s">
+        <v>163</v>
+      </c>
+      <c r="C230" t="s">
+        <v>239</v>
+      </c>
+      <c r="D230" t="s">
+        <v>455</v>
+      </c>
+      <c r="E230" t="s">
+        <v>9</v>
+      </c>
+      <c r="F230" t="s">
+        <v>16</v>
+      </c>
+      <c r="G230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231">
+        <v>23330051920122</v>
+      </c>
+      <c r="B231" t="s">
+        <v>139</v>
+      </c>
+      <c r="C231" t="s">
+        <v>185</v>
+      </c>
+      <c r="D231" t="s">
+        <v>456</v>
+      </c>
+      <c r="E231" t="s">
+        <v>9</v>
+      </c>
+      <c r="F231" t="s">
+        <v>16</v>
+      </c>
+      <c r="G231">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232">
+        <v>23330051920140</v>
+      </c>
+      <c r="B232" t="s">
+        <v>164</v>
+      </c>
+      <c r="C232" t="s">
+        <v>94</v>
+      </c>
+      <c r="D232" t="s">
+        <v>457</v>
+      </c>
+      <c r="E232" t="s">
+        <v>9</v>
+      </c>
+      <c r="F232" t="s">
+        <v>16</v>
+      </c>
+      <c r="G232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233">
+        <v>23330051920139</v>
+      </c>
+      <c r="B233" t="s">
+        <v>47</v>
+      </c>
+      <c r="C233" t="s">
+        <v>107</v>
+      </c>
+      <c r="D233" t="s">
+        <v>458</v>
+      </c>
+      <c r="E233" t="s">
+        <v>9</v>
+      </c>
+      <c r="F233" t="s">
+        <v>16</v>
+      </c>
+      <c r="G233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234">
+        <v>23330051920138</v>
+      </c>
+      <c r="B234" t="s">
+        <v>39</v>
+      </c>
+      <c r="C234" t="s">
+        <v>240</v>
+      </c>
+      <c r="D234" t="s">
+        <v>459</v>
+      </c>
+      <c r="E234" t="s">
+        <v>9</v>
+      </c>
+      <c r="F234" t="s">
+        <v>16</v>
+      </c>
+      <c r="G234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235">
+        <v>23330051920255</v>
+      </c>
+      <c r="B235" t="s">
+        <v>128</v>
+      </c>
+      <c r="C235" t="s">
+        <v>241</v>
+      </c>
+      <c r="D235" t="s">
+        <v>460</v>
+      </c>
+      <c r="E235" t="s">
+        <v>9</v>
+      </c>
+      <c r="F235" t="s">
+        <v>16</v>
+      </c>
+      <c r="G235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236">
+        <v>23330051920141</v>
+      </c>
+      <c r="B236" t="s">
+        <v>49</v>
+      </c>
+      <c r="C236" t="s">
+        <v>242</v>
+      </c>
+      <c r="D236" t="s">
+        <v>461</v>
+      </c>
+      <c r="E236" t="s">
+        <v>9</v>
+      </c>
+      <c r="F236" t="s">
+        <v>16</v>
+      </c>
+      <c r="G236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237">
+        <v>23330051920315</v>
+      </c>
+      <c r="B237" t="s">
+        <v>97</v>
+      </c>
+      <c r="C237" t="s">
+        <v>243</v>
+      </c>
+      <c r="D237" t="s">
+        <v>462</v>
+      </c>
+      <c r="E237" t="s">
+        <v>9</v>
+      </c>
+      <c r="F237" t="s">
+        <v>16</v>
+      </c>
+      <c r="G237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238">
+        <v>23330051920142</v>
+      </c>
+      <c r="B238" t="s">
+        <v>60</v>
+      </c>
+      <c r="C238" t="s">
+        <v>75</v>
+      </c>
+      <c r="D238" t="s">
+        <v>463</v>
+      </c>
+      <c r="E238" t="s">
+        <v>9</v>
+      </c>
+      <c r="F238" t="s">
+        <v>16</v>
+      </c>
+      <c r="G238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239">
+        <v>23330051920143</v>
+      </c>
+      <c r="B239" t="s">
+        <v>57</v>
+      </c>
+      <c r="C239" t="s">
+        <v>230</v>
+      </c>
+      <c r="D239" t="s">
+        <v>464</v>
+      </c>
+      <c r="E239" t="s">
+        <v>9</v>
+      </c>
+      <c r="F239" t="s">
+        <v>16</v>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240">
+        <v>23330051920146</v>
+      </c>
+      <c r="B240" t="s">
+        <v>70</v>
+      </c>
+      <c r="C240" t="s">
+        <v>33</v>
+      </c>
+      <c r="D240" t="s">
+        <v>465</v>
+      </c>
+      <c r="E240" t="s">
+        <v>9</v>
+      </c>
+      <c r="F240" t="s">
+        <v>16</v>
+      </c>
+      <c r="G240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241">
+        <v>23330051920147</v>
+      </c>
+      <c r="B241" t="s">
+        <v>153</v>
+      </c>
+      <c r="C241" t="s">
+        <v>244</v>
+      </c>
+      <c r="D241" t="s">
+        <v>466</v>
+      </c>
+      <c r="E241" t="s">
+        <v>9</v>
+      </c>
+      <c r="F241" t="s">
+        <v>16</v>
+      </c>
+      <c r="G241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242">
+        <v>23330051920346</v>
+      </c>
+      <c r="B242" t="s">
+        <v>165</v>
+      </c>
+      <c r="C242" t="s">
+        <v>79</v>
+      </c>
+      <c r="D242" t="s">
+        <v>467</v>
+      </c>
+      <c r="E242" t="s">
+        <v>9</v>
+      </c>
+      <c r="F242" t="s">
+        <v>16</v>
+      </c>
+      <c r="G242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243">
+        <v>23330051920148</v>
+      </c>
+      <c r="B243" t="s">
+        <v>166</v>
+      </c>
+      <c r="C243" t="s">
+        <v>33</v>
+      </c>
+      <c r="D243" t="s">
+        <v>468</v>
+      </c>
+      <c r="E243" t="s">
+        <v>9</v>
+      </c>
+      <c r="F243" t="s">
+        <v>16</v>
+      </c>
+      <c r="G243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244">
         <v>23330051920149</v>
       </c>
-      <c r="B210" t="s">
-        <v>152</v>
-      </c>
-      <c r="C210" t="s">
-        <v>226</v>
-      </c>
-      <c r="D210" t="s">
-        <v>419</v>
-      </c>
-      <c r="E210" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210" t="s">
+      <c r="B244" t="s">
+        <v>167</v>
+      </c>
+      <c r="C244" t="s">
+        <v>245</v>
+      </c>
+      <c r="D244" t="s">
+        <v>469</v>
+      </c>
+      <c r="E244" t="s">
+        <v>9</v>
+      </c>
+      <c r="F244" t="s">
         <v>16</v>
       </c>
-      <c r="G210">
+      <c r="G244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245">
+        <v>23330051920150</v>
+      </c>
+      <c r="B245" t="s">
+        <v>32</v>
+      </c>
+      <c r="C245" t="s">
+        <v>56</v>
+      </c>
+      <c r="D245" t="s">
+        <v>470</v>
+      </c>
+      <c r="E245" t="s">
+        <v>9</v>
+      </c>
+      <c r="F245" t="s">
+        <v>16</v>
+      </c>
+      <c r="G245">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Faltante Faltante Faltante - Estadisticos 20241.xlsx
+++ b/docentes/Faltante Faltante Faltante - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="476">
   <si>
     <t>Mat</t>
   </si>
@@ -178,210 +178,216 @@
     <t>ZACARIAS</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>COCOTLE</t>
+    <t>BERULES</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BALCAZAR</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BERULES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>AZPIRI</t>
-  </si>
-  <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ABREGO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BALCAZAR</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>ARENAS</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
@@ -427,9 +433,6 @@
     <t>CALVA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -556,144 +559,147 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>MIXTECO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TOLENTINO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>TENCHIPE</t>
+  </si>
+  <si>
+    <t>CORREA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>POOT</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>AUTRAN</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>MIXTECO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>MONDRAGON</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>CALCANEO</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>TINOCO</t>
   </si>
   <si>
@@ -844,451 +850,460 @@
     <t>ANGEL ABRAHAM</t>
   </si>
   <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>PABLO AZAEL</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
+  </si>
+  <si>
+    <t>OSMAR EDUARDO</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>ERICK ANGEL</t>
+  </si>
+  <si>
+    <t>VICENTE ABIMAEL</t>
+  </si>
+  <si>
+    <t>DANA INGRID</t>
+  </si>
+  <si>
+    <t>OMAR DAVID</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>DANILO</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOEL MIGUEL</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ANGEL NAIN</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
+    <t>MARIAM MICHAELL</t>
+  </si>
+  <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>ALEX TADEO</t>
+  </si>
+  <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
+    <t>ANGEL EDUC</t>
+  </si>
+  <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
+    <t>ARELI DANAE</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANIELA SAMANTA</t>
+  </si>
+  <si>
+    <t>CONCEPCION GUADALUPE</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>DAFNE</t>
+  </si>
+  <si>
+    <t>HEIDI</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>GUADALUPE ANAHI</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>RAMSES</t>
+  </si>
+  <si>
+    <t>FRANCISCO XAVIER</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>SAMIR</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>MIREILLE</t>
+  </si>
+  <si>
+    <t>SULU ALAN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>XOCHITL ALELI</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>KEIRA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>KENYA MARIANA</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>SALMA JANET</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
+    <t>ELIUD EDUARDO</t>
+  </si>
+  <si>
+    <t>KAORY AYELEN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>HUGO ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>JURISEL</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
+  </si>
+  <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>YURI MONSERRAT</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>INGRID ISABEL</t>
+  </si>
+  <si>
+    <t>MAR EDITH</t>
+  </si>
+  <si>
+    <t>MELISA</t>
+  </si>
+  <si>
+    <t>JUAN ALONSO</t>
+  </si>
+  <si>
+    <t>CRIZULY AMITHAI</t>
+  </si>
+  <si>
+    <t>ADIEL ALONSO</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>EUNICE</t>
+  </si>
+  <si>
+    <t>REYNA IVETT</t>
+  </si>
+  <si>
+    <t>HANNA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>KAROL BALAAM</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>YASMIN</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
+  </si>
+  <si>
+    <t>ROSA EVELYN</t>
+  </si>
+  <si>
+    <t>VANIA</t>
+  </si>
+  <si>
+    <t>DARLA AMERICA</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>DIANA PAOLA</t>
+  </si>
+  <si>
+    <t>MARIEL BIDEMI</t>
+  </si>
+  <si>
+    <t>CARMEN VANELI</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>LORENA</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
     <t>JOSUE</t>
   </si>
   <si>
-    <t>PAOLA</t>
+    <t>LUZ YESENIA</t>
+  </si>
+  <si>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>XIMENA ISABEL</t>
+  </si>
+  <si>
+    <t>NURIA BELEN</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>BRISEIDA</t>
+  </si>
+  <si>
+    <t>DORIAN</t>
+  </si>
+  <si>
+    <t>VICTORIA VIANNEY</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>VIANEY SAMARI</t>
+  </si>
+  <si>
+    <t>CLARA LIZBETH</t>
+  </si>
+  <si>
+    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>PABLO AZAEL</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
-  </si>
-  <si>
-    <t>OSMAR EDUARDO</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>ERICK ANGEL</t>
-  </si>
-  <si>
-    <t>VICENTE ABIMAEL</t>
-  </si>
-  <si>
-    <t>DANA INGRID</t>
-  </si>
-  <si>
-    <t>OMAR DAVID</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>FELIX</t>
-  </si>
-  <si>
-    <t>DANILO</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>AXEL AARON</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>ANGEL NAIN</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>MARIAM MICHAELL</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>ALEX TADEO</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>ARELI DANAE</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
-  </si>
-  <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>GUADALUPE ANAHI</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>RAMSES</t>
-  </si>
-  <si>
-    <t>FRANCISCO XAVIER</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>MARYSOL</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>ANGEL ADRIAN</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>MIREILLE</t>
-  </si>
-  <si>
-    <t>SULU ALAN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEVIN IVAN</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ABRAHAN</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>YURI MONSERRAT</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAELIS</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>INGRID ISABEL</t>
-  </si>
-  <si>
-    <t>MAR EDITH</t>
-  </si>
-  <si>
-    <t>MELISA</t>
-  </si>
-  <si>
-    <t>JUAN ALONSO</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>ADIEL ALONSO</t>
-  </si>
-  <si>
-    <t>LLUVIA ITZEL</t>
-  </si>
-  <si>
-    <t>EUNICE</t>
-  </si>
-  <si>
-    <t>REYNA IVETT</t>
-  </si>
-  <si>
-    <t>HANNA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>ROSA EVELYN</t>
-  </si>
-  <si>
-    <t>VANIA</t>
-  </si>
-  <si>
-    <t>DARLA AMERICA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>DIANA PAOLA</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>CARMEN VANELI</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>ANGEL JESUS</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>XIMENA ISABEL</t>
-  </si>
-  <si>
-    <t>NURIA BELEN</t>
-  </si>
-  <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>BRISEIDA</t>
-  </si>
-  <si>
-    <t>DORIAN</t>
-  </si>
-  <si>
-    <t>VICTORIA VIANNEY</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>VIANEY SAMARI</t>
-  </si>
-  <si>
-    <t>CLARA LIZBETH</t>
-  </si>
-  <si>
-    <t>HEIDI KESEI</t>
   </si>
   <si>
     <t>JULIO ALBERTO</t>
@@ -2807,7 +2822,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G245"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -2848,7 +2863,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -2868,10 +2883,10 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2891,10 +2906,10 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -2914,10 +2929,10 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -2940,7 +2955,7 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -2960,10 +2975,10 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -2983,10 +2998,10 @@
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -3006,10 +3021,10 @@
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3029,10 +3044,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -3052,10 +3067,10 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -3075,10 +3090,10 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -3101,7 +3116,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -3124,7 +3139,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -3147,7 +3162,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -3170,7 +3185,7 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -3190,10 +3205,10 @@
         <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -3213,10 +3228,10 @@
         <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -3236,10 +3251,10 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -3259,10 +3274,10 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -3282,10 +3297,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -3305,10 +3320,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -3328,10 +3343,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -3351,10 +3366,10 @@
         <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -3377,7 +3392,7 @@
         <v>43</v>
       </c>
       <c r="D25" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -3397,10 +3412,10 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -3420,10 +3435,10 @@
         <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -3443,10 +3458,10 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D28" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -3466,10 +3481,10 @@
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D29" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -3489,10 +3504,10 @@
         <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -3506,16 +3521,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920319</v>
+        <v>23330051920339</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="D31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -3529,16 +3544,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920339</v>
+        <v>23330051920303</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -3552,22 +3567,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920289</v>
+        <v>23330051920181</v>
       </c>
       <c r="B33" t="s">
         <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D33" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -3575,22 +3590,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920303</v>
+        <v>22330051920007</v>
       </c>
       <c r="B34" t="s">
         <v>56</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -3604,10 +3619,10 @@
         <v>57</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -3621,22 +3636,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920144</v>
+        <v>23330051920212</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="D36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -3644,62 +3659,62 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920012</v>
+        <v>22330061460232</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="D37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920025</v>
+        <v>23330051920144</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>24330051920027</v>
+        <v>24330051920012</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D39" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -3713,16 +3728,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>24330051920001</v>
+        <v>24330051920025</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D40" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -3736,22 +3751,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920003</v>
+        <v>24330051920027</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -3759,22 +3774,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920002</v>
+        <v>24330051920001</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3782,16 +3797,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920004</v>
+        <v>23330051920003</v>
       </c>
       <c r="B43" t="s">
         <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>182</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -3805,16 +3820,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920005</v>
+        <v>23330051920002</v>
       </c>
       <c r="B44" t="s">
         <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -3828,16 +3843,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920182</v>
+        <v>23330051920004</v>
       </c>
       <c r="B45" t="s">
         <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="D45" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
@@ -3851,16 +3866,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920009</v>
+        <v>23330051920005</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>186</v>
       </c>
       <c r="D46" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E46" t="s">
         <v>9</v>
@@ -3874,16 +3889,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920026</v>
+        <v>23330051920182</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -3897,16 +3912,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920010</v>
+        <v>23330051920009</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
@@ -3920,16 +3935,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920012</v>
+        <v>23330051920026</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E49" t="s">
         <v>9</v>
@@ -3943,16 +3958,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920013</v>
+        <v>23330051920010</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -3966,16 +3981,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920014</v>
+        <v>23330051920012</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E51" t="s">
         <v>9</v>
@@ -3989,16 +4004,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920204</v>
+        <v>23330051920013</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E52" t="s">
         <v>9</v>
@@ -4012,16 +4027,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920321</v>
+        <v>23330051920014</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="D53" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E53" t="s">
         <v>9</v>
@@ -4035,16 +4050,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>23330051920021</v>
+        <v>23330051920204</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="D54" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
@@ -4058,16 +4073,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>23330051920020</v>
+        <v>23330051920321</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="D55" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
@@ -4081,16 +4096,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>23330051920024</v>
+        <v>23330051920021</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -4104,22 +4119,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>23330051920179</v>
+        <v>23330051920020</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C57" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D57" t="s">
-        <v>199</v>
+        <v>302</v>
       </c>
       <c r="E57" t="s">
         <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -4127,22 +4142,22 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>23330051920180</v>
+        <v>23330051920024</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D58" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E58" t="s">
         <v>9</v>
       </c>
       <c r="F58" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -4150,16 +4165,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>23330051920190</v>
+        <v>23330051920179</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
         <v>9</v>
@@ -4173,16 +4188,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>23330051920199</v>
+        <v>23330051920180</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
         <v>84</v>
       </c>
       <c r="D60" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -4196,16 +4211,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>23330051920206</v>
+        <v>23330051920190</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="D61" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -4219,16 +4234,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>23330051920186</v>
+        <v>23330051920199</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -4242,22 +4257,22 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>23330051920078</v>
+        <v>23330051920206</v>
       </c>
       <c r="B63" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E63" t="s">
         <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -4265,22 +4280,22 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>23330051920077</v>
+        <v>23330051920186</v>
       </c>
       <c r="B64" t="s">
         <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -4288,16 +4303,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>23330051920079</v>
+        <v>23330051920078</v>
       </c>
       <c r="B65" t="s">
         <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>43</v>
       </c>
       <c r="D65" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
@@ -4311,16 +4326,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>23330051920080</v>
+        <v>23330051920077</v>
       </c>
       <c r="B66" t="s">
         <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D66" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
@@ -4334,16 +4349,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>23330051920082</v>
+        <v>23330051920079</v>
       </c>
       <c r="B67" t="s">
         <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" t="s">
-        <v>268</v>
+        <v>311</v>
       </c>
       <c r="E67" t="s">
         <v>9</v>
@@ -4357,16 +4372,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>23330051920085</v>
+        <v>23330051920080</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="D68" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -4380,16 +4395,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>23330051920086</v>
+        <v>23330051920082</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="D69" t="s">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="E69" t="s">
         <v>9</v>
@@ -4403,16 +4418,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>23330051920084</v>
+        <v>23330051920085</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E70" t="s">
         <v>9</v>
@@ -4426,16 +4441,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>23330051920087</v>
+        <v>23330051920086</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C71" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D71" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E71" t="s">
         <v>9</v>
@@ -4449,16 +4464,16 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>23330051920088</v>
+        <v>23330051920084</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D72" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -4472,16 +4487,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>23330051920089</v>
+        <v>23330051920087</v>
       </c>
       <c r="B73" t="s">
         <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="D73" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E73" t="s">
         <v>9</v>
@@ -4495,16 +4510,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>23330051920090</v>
+        <v>23330051920088</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D74" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -4518,16 +4533,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>23330051920091</v>
+        <v>23330051920089</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C75" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="D75" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E75" t="s">
         <v>9</v>
@@ -4541,16 +4556,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>23330051920234</v>
+        <v>23330051920090</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="D76" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E76" t="s">
         <v>9</v>
@@ -4564,16 +4579,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>23330051920094</v>
+        <v>23330051920091</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D77" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E77" t="s">
         <v>9</v>
@@ -4587,16 +4602,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>23330051920099</v>
+        <v>23330051920234</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D78" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E78" t="s">
         <v>9</v>
@@ -4610,16 +4625,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>23330051920098</v>
+        <v>23330051920094</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="D79" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E79" t="s">
         <v>9</v>
@@ -4633,16 +4648,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>23330051920100</v>
+        <v>23330051920099</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="D80" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
@@ -4656,16 +4671,16 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>23330051920102</v>
+        <v>23330051920098</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="D81" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E81" t="s">
         <v>9</v>
@@ -4679,16 +4694,16 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>23330051920103</v>
+        <v>23330051920100</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D82" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -4702,16 +4717,16 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>23330051920104</v>
+        <v>23330051920102</v>
       </c>
       <c r="B83" t="s">
         <v>86</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E83" t="s">
         <v>9</v>
@@ -4725,16 +4740,16 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>23330051920261</v>
+        <v>23330051920103</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C84" t="s">
-        <v>196</v>
+        <v>54</v>
       </c>
       <c r="D84" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
@@ -4748,16 +4763,16 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>23330051920106</v>
+        <v>23330051920104</v>
       </c>
       <c r="B85" t="s">
         <v>87</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="D85" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E85" t="s">
         <v>9</v>
@@ -4771,16 +4786,16 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>23330051920107</v>
+        <v>23330051920261</v>
       </c>
       <c r="B86" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C86" t="s">
-        <v>45</v>
+        <v>199</v>
       </c>
       <c r="D86" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
@@ -4794,16 +4809,16 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>23330051920108</v>
+        <v>23330051920106</v>
       </c>
       <c r="B87" t="s">
         <v>88</v>
       </c>
       <c r="C87" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="D87" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E87" t="s">
         <v>9</v>
@@ -4817,16 +4832,16 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>23330051920110</v>
+        <v>23330051920107</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C88" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E88" t="s">
         <v>9</v>
@@ -4840,16 +4855,16 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>23330051920114</v>
+        <v>23330051920108</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>56</v>
+        <v>200</v>
       </c>
       <c r="D89" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E89" t="s">
         <v>9</v>
@@ -4863,16 +4878,16 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>23330051920115</v>
+        <v>23330051920110</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
@@ -4886,22 +4901,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>23330051920218</v>
+        <v>23330051920114</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D91" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E91" t="s">
         <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -4909,22 +4924,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>23330051920221</v>
+        <v>23330051920115</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="D92" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -4932,16 +4947,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>23330051920223</v>
+        <v>23330051920218</v>
       </c>
       <c r="B93" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="D93" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E93" t="s">
         <v>9</v>
@@ -4955,16 +4970,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>23330051920229</v>
+        <v>23330051920221</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="D94" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E94" t="s">
         <v>9</v>
@@ -4978,16 +4993,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>23330051920241</v>
+        <v>23330051920223</v>
       </c>
       <c r="B95" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C95" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="D95" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
@@ -5001,16 +5016,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>23330051920335</v>
+        <v>23330051920229</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C96" t="s">
-        <v>53</v>
+        <v>202</v>
       </c>
       <c r="D96" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E96" t="s">
         <v>9</v>
@@ -5024,16 +5039,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>23330051920245</v>
+        <v>23330051920241</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E97" t="s">
         <v>9</v>
@@ -5047,16 +5062,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>23330051920247</v>
+        <v>23330051920335</v>
       </c>
       <c r="B98" t="s">
         <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="D98" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E98" t="s">
         <v>9</v>
@@ -5070,16 +5085,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>23330051920249</v>
+        <v>23330051920245</v>
       </c>
       <c r="B99" t="s">
         <v>95</v>
       </c>
       <c r="C99" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
       <c r="D99" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E99" t="s">
         <v>9</v>
@@ -5093,16 +5108,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>23330051920253</v>
+        <v>23330051920247</v>
       </c>
       <c r="B100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D100" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E100" t="s">
         <v>9</v>
@@ -5116,13 +5131,13 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>23330051920318</v>
+        <v>23330051920249</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C101" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="D101" t="s">
         <v>341</v>
@@ -5139,16 +5154,16 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>23330051920258</v>
+        <v>23330051920253</v>
       </c>
       <c r="B102" t="s">
         <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>106</v>
+        <v>204</v>
       </c>
       <c r="D102" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
@@ -5162,16 +5177,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>23330051920264</v>
+        <v>23330051920318</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C103" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="D103" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E103" t="s">
         <v>9</v>
@@ -5185,16 +5200,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>23330051920265</v>
+        <v>23330051920258</v>
       </c>
       <c r="B104" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C104" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D104" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E104" t="s">
         <v>9</v>
@@ -5208,16 +5223,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>23330051920267</v>
+        <v>23330051920264</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="D105" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E105" t="s">
         <v>9</v>
@@ -5231,16 +5246,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>23330051920273</v>
+        <v>23330051920265</v>
       </c>
       <c r="B106" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="D106" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
@@ -5254,22 +5269,22 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107">
-        <v>23330051920151</v>
+        <v>23330051920267</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="C107" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="D107" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E107" t="s">
         <v>9</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -5277,22 +5292,22 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>23330051920152</v>
+        <v>23330051920273</v>
       </c>
       <c r="B108" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C108" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="D108" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E108" t="s">
         <v>9</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -5300,16 +5315,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>23330051920153</v>
+        <v>23330051920151</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C109" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="D109" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E109" t="s">
         <v>9</v>
@@ -5323,16 +5338,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>23330051920155</v>
+        <v>23330051920152</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C110" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D110" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E110" t="s">
         <v>9</v>
@@ -5346,16 +5361,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>23330051920154</v>
+        <v>23330051920153</v>
       </c>
       <c r="B111" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="C111" t="s">
-        <v>205</v>
+        <v>40</v>
       </c>
       <c r="D111" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E111" t="s">
         <v>9</v>
@@ -5369,16 +5384,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>23330051920325</v>
+        <v>23330051920155</v>
       </c>
       <c r="B112" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D112" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E112" t="s">
         <v>9</v>
@@ -5392,16 +5407,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>23330051920250</v>
+        <v>23330051920154</v>
       </c>
       <c r="B113" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C113" t="s">
-        <v>97</v>
+        <v>208</v>
       </c>
       <c r="D113" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E113" t="s">
         <v>9</v>
@@ -5415,16 +5430,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>23330051920157</v>
+        <v>23330051920325</v>
       </c>
       <c r="B114" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C114" t="s">
-        <v>57</v>
+        <v>209</v>
       </c>
       <c r="D114" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E114" t="s">
         <v>9</v>
@@ -5438,16 +5453,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>23330051920158</v>
+        <v>23330051920250</v>
       </c>
       <c r="B115" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C115" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D115" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E115" t="s">
         <v>9</v>
@@ -5461,16 +5476,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>23330051920159</v>
+        <v>23330051920157</v>
       </c>
       <c r="B116" t="s">
         <v>43</v>
       </c>
       <c r="C116" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D116" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E116" t="s">
         <v>9</v>
@@ -5484,16 +5499,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>23330051920161</v>
+        <v>23330051920158</v>
       </c>
       <c r="B117" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C117" t="s">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="D117" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E117" t="s">
         <v>9</v>
@@ -5507,16 +5522,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>23330051920162</v>
+        <v>23330051920159</v>
       </c>
       <c r="B118" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C118" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="D118" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E118" t="s">
         <v>9</v>
@@ -5530,16 +5545,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>23330051920163</v>
+        <v>23330051920161</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="C119" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D119" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E119" t="s">
         <v>9</v>
@@ -5553,16 +5568,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>23330051920164</v>
+        <v>23330051920162</v>
       </c>
       <c r="B120" t="s">
         <v>104</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D120" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E120" t="s">
         <v>9</v>
@@ -5576,16 +5591,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>23330051920297</v>
+        <v>23330051920163</v>
       </c>
       <c r="B121" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C121" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="D121" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E121" t="s">
         <v>9</v>
@@ -5599,16 +5614,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>23330051920165</v>
+        <v>23330051920164</v>
       </c>
       <c r="B122" t="s">
         <v>105</v>
       </c>
       <c r="C122" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="D122" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E122" t="s">
         <v>9</v>
@@ -5622,16 +5637,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>23330051920166</v>
+        <v>23330051920297</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="C123" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D123" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E123" t="s">
         <v>9</v>
@@ -5645,16 +5660,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>23330051920167</v>
+        <v>23330051920165</v>
       </c>
       <c r="B124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C124" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D124" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E124" t="s">
         <v>9</v>
@@ -5668,16 +5683,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>23330051920310</v>
+        <v>23330051920166</v>
       </c>
       <c r="B125" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="D125" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E125" t="s">
         <v>9</v>
@@ -5691,16 +5706,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>23330051920169</v>
+        <v>23330051920167</v>
       </c>
       <c r="B126" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C126" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="D126" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E126" t="s">
         <v>9</v>
@@ -5714,16 +5729,16 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>23330051920354</v>
+        <v>23330051920310</v>
       </c>
       <c r="B127" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C127" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D127" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E127" t="s">
         <v>9</v>
@@ -5737,16 +5752,16 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>23330051920170</v>
+        <v>23330051920169</v>
       </c>
       <c r="B128" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C128" t="s">
-        <v>209</v>
+        <v>123</v>
       </c>
       <c r="D128" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E128" t="s">
         <v>9</v>
@@ -5760,16 +5775,16 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
-        <v>23330051920173</v>
+        <v>23330051920354</v>
       </c>
       <c r="B129" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C129" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E129" t="s">
         <v>9</v>
@@ -5783,16 +5798,16 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130">
-        <v>23330051920172</v>
+        <v>23330051920170</v>
       </c>
       <c r="B130" t="s">
         <v>109</v>
       </c>
       <c r="C130" t="s">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="E130" t="s">
         <v>9</v>
@@ -5806,16 +5821,16 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131">
-        <v>23330051920311</v>
+        <v>23330051920173</v>
       </c>
       <c r="B131" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="C131" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D131" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E131" t="s">
         <v>9</v>
@@ -5829,16 +5844,16 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132">
-        <v>23330051920174</v>
+        <v>23330051920172</v>
       </c>
       <c r="B132" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="C132" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D132" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
       <c r="E132" t="s">
         <v>9</v>
@@ -5852,22 +5867,22 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133">
-        <v>23330051920281</v>
+        <v>23330051920311</v>
       </c>
       <c r="B133" t="s">
         <v>111</v>
       </c>
       <c r="C133" t="s">
-        <v>210</v>
+        <v>33</v>
       </c>
       <c r="D133" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E133" t="s">
         <v>9</v>
       </c>
       <c r="F133" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G133">
         <v>1</v>
@@ -5875,22 +5890,22 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134">
-        <v>23330051920283</v>
+        <v>23330051920174</v>
       </c>
       <c r="B134" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C134" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D134" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E134" t="s">
         <v>9</v>
       </c>
       <c r="F134" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -5898,16 +5913,16 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135">
-        <v>23330051920284</v>
+        <v>23330051920281</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C135" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D135" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E135" t="s">
         <v>9</v>
@@ -5921,16 +5936,16 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136">
-        <v>23330051920292</v>
+        <v>23330051920283</v>
       </c>
       <c r="B136" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="C136" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D136" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E136" t="s">
         <v>9</v>
@@ -5944,16 +5959,16 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137">
-        <v>23330051920365</v>
+        <v>23330051920284</v>
       </c>
       <c r="B137" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C137" t="s">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="D137" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E137" t="s">
         <v>9</v>
@@ -5967,16 +5982,16 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138">
-        <v>23330051920296</v>
+        <v>23330051920292</v>
       </c>
       <c r="B138" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="D138" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E138" t="s">
         <v>9</v>
@@ -5990,16 +6005,16 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139">
-        <v>23330051920299</v>
+        <v>23330051920365</v>
       </c>
       <c r="B139" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C139" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="D139" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E139" t="s">
         <v>9</v>
@@ -6013,16 +6028,16 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140">
-        <v>23330051920308</v>
+        <v>23330051920296</v>
       </c>
       <c r="B140" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C140" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="D140" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E140" t="s">
         <v>9</v>
@@ -6036,16 +6051,16 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141">
-        <v>23330051920348</v>
+        <v>23330051920299</v>
       </c>
       <c r="B141" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="C141" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D141" t="s">
-        <v>302</v>
+        <v>381</v>
       </c>
       <c r="E141" t="s">
         <v>9</v>
@@ -6059,16 +6074,16 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142">
-        <v>23330051920363</v>
+        <v>23330051920308</v>
       </c>
       <c r="B142" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="C142" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D142" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E142" t="s">
         <v>9</v>
@@ -6082,16 +6097,16 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143">
-        <v>23330051920326</v>
+        <v>23330051920348</v>
       </c>
       <c r="B143" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C143" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D143" t="s">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
@@ -6105,22 +6120,22 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144">
-        <v>23330051920048</v>
+        <v>23330051920363</v>
       </c>
       <c r="B144" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="C144" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="D144" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E144" t="s">
         <v>9</v>
       </c>
       <c r="F144" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -6128,22 +6143,22 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145">
-        <v>23330051920049</v>
+        <v>23330051920326</v>
       </c>
       <c r="B145" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C145" t="s">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="D145" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E145" t="s">
         <v>9</v>
       </c>
       <c r="F145" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -6151,16 +6166,16 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>23330051920050</v>
+        <v>23330051920048</v>
       </c>
       <c r="B146" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C146" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="D146" t="s">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="E146" t="s">
         <v>9</v>
@@ -6174,16 +6189,16 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>23330051920083</v>
+        <v>23330051920049</v>
       </c>
       <c r="B147" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C147" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="D147" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E147" t="s">
         <v>9</v>
@@ -6197,16 +6212,16 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>23330051920053</v>
+        <v>23330051920050</v>
       </c>
       <c r="B148" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C148" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="D148" t="s">
-        <v>384</v>
+        <v>277</v>
       </c>
       <c r="E148" t="s">
         <v>9</v>
@@ -6220,16 +6235,16 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>23330051920227</v>
+        <v>23330051920083</v>
       </c>
       <c r="B149" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C149" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="D149" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E149" t="s">
         <v>9</v>
@@ -6243,16 +6258,16 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
-        <v>23330051920054</v>
+        <v>23330051920053</v>
       </c>
       <c r="B150" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>195</v>
       </c>
       <c r="D150" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E150" t="s">
         <v>9</v>
@@ -6266,16 +6281,16 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
-        <v>23330051920055</v>
+        <v>23330051920227</v>
       </c>
       <c r="B151" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="C151" t="s">
-        <v>44</v>
+        <v>182</v>
       </c>
       <c r="D151" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E151" t="s">
         <v>9</v>
@@ -6289,16 +6304,16 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152">
-        <v>23330051920056</v>
+        <v>23330051920054</v>
       </c>
       <c r="B152" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C152" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D152" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E152" t="s">
         <v>9</v>
@@ -6312,16 +6327,16 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153">
-        <v>23330051920057</v>
+        <v>23330051920055</v>
       </c>
       <c r="B153" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="C153" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D153" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E153" t="s">
         <v>9</v>
@@ -6335,16 +6350,16 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154">
-        <v>23330051920058</v>
+        <v>23330051920056</v>
       </c>
       <c r="B154" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C154" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="D154" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E154" t="s">
         <v>9</v>
@@ -6358,16 +6373,16 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>23330051920246</v>
+        <v>23330051920057</v>
       </c>
       <c r="B155" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="C155" t="s">
-        <v>215</v>
+        <v>47</v>
       </c>
       <c r="D155" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E155" t="s">
         <v>9</v>
@@ -6381,16 +6396,16 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>23330051920060</v>
+        <v>23330051920058</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C156" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="D156" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E156" t="s">
         <v>9</v>
@@ -6404,16 +6419,16 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>23330051920061</v>
+        <v>23330051920246</v>
       </c>
       <c r="B157" t="s">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="C157" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D157" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
@@ -6427,16 +6442,16 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>23330051920062</v>
+        <v>23330051920060</v>
       </c>
       <c r="B158" t="s">
         <v>126</v>
       </c>
       <c r="C158" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D158" t="s">
-        <v>324</v>
+        <v>396</v>
       </c>
       <c r="E158" t="s">
         <v>9</v>
@@ -6450,16 +6465,16 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>23330051920307</v>
+        <v>23330051920061</v>
       </c>
       <c r="B159" t="s">
         <v>127</v>
       </c>
       <c r="C159" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D159" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="E159" t="s">
         <v>9</v>
@@ -6473,16 +6488,16 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>23330051920063</v>
+        <v>23330051920062</v>
       </c>
       <c r="B160" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="C160" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D160" t="s">
-        <v>394</v>
+        <v>328</v>
       </c>
       <c r="E160" t="s">
         <v>9</v>
@@ -6496,16 +6511,16 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>23330051920064</v>
+        <v>23330051920307</v>
       </c>
       <c r="B161" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="C161" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="D161" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="E161" t="s">
         <v>9</v>
@@ -6519,16 +6534,16 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>23330051920260</v>
+        <v>23330051920063</v>
       </c>
       <c r="B162" t="s">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="C162" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="D162" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E162" t="s">
         <v>9</v>
@@ -6542,16 +6557,16 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>23330051920066</v>
+        <v>23330051920064</v>
       </c>
       <c r="B163" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="C163" t="s">
-        <v>207</v>
+        <v>57</v>
       </c>
       <c r="D163" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E163" t="s">
         <v>9</v>
@@ -6565,16 +6580,16 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>23330051920067</v>
+        <v>23330051920260</v>
       </c>
       <c r="B164" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C164" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D164" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E164" t="s">
         <v>9</v>
@@ -6588,16 +6603,16 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
-        <v>23330051920068</v>
+        <v>23330051920066</v>
       </c>
       <c r="B165" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C165" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="D165" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E165" t="s">
         <v>9</v>
@@ -6611,16 +6626,16 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166">
-        <v>23330051920069</v>
+        <v>23330051920067</v>
       </c>
       <c r="B166" t="s">
         <v>131</v>
       </c>
       <c r="C166" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D166" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
@@ -6634,16 +6649,16 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167">
-        <v>23330051920070</v>
+        <v>23330051920068</v>
       </c>
       <c r="B167" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="C167" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D167" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E167" t="s">
         <v>9</v>
@@ -6657,16 +6672,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168">
-        <v>23330051920330</v>
+        <v>23330051920069</v>
       </c>
       <c r="B168" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="C168" t="s">
-        <v>83</v>
+        <v>222</v>
       </c>
       <c r="D168" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E168" t="s">
         <v>9</v>
@@ -6680,16 +6695,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169">
-        <v>23330051920272</v>
+        <v>23330051920070</v>
       </c>
       <c r="B169" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C169" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="D169" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E169" t="s">
         <v>9</v>
@@ -6703,16 +6718,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170">
-        <v>23330051920073</v>
+        <v>23330051920330</v>
       </c>
       <c r="B170" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C170" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="D170" t="s">
-        <v>404</v>
+        <v>280</v>
       </c>
       <c r="E170" t="s">
         <v>9</v>
@@ -6726,16 +6741,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171">
-        <v>23330051920074</v>
+        <v>23330051920272</v>
       </c>
       <c r="B171" t="s">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="C171" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="D171" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E171" t="s">
         <v>9</v>
@@ -6749,16 +6764,16 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172">
-        <v>23330051920075</v>
+        <v>23330051920073</v>
       </c>
       <c r="B172" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="C172" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D172" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E172" t="s">
         <v>9</v>
@@ -6772,22 +6787,22 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173">
-        <v>23330051920213</v>
+        <v>23330051920074</v>
       </c>
       <c r="B173" t="s">
         <v>134</v>
       </c>
       <c r="C173" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="D173" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E173" t="s">
         <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -6795,22 +6810,22 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174">
-        <v>23330051920226</v>
+        <v>23330051920075</v>
       </c>
       <c r="B174" t="s">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="C174" t="s">
-        <v>222</v>
+        <v>38</v>
       </c>
       <c r="D174" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E174" t="s">
         <v>9</v>
       </c>
       <c r="F174" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -6818,16 +6833,16 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175">
-        <v>23330051920215</v>
+        <v>23330051920213</v>
       </c>
       <c r="B175" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C175" t="s">
-        <v>110</v>
+        <v>223</v>
       </c>
       <c r="D175" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E175" t="s">
         <v>9</v>
@@ -6841,16 +6856,16 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176">
-        <v>23330051920216</v>
+        <v>23330051920226</v>
       </c>
       <c r="B176" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="C176" t="s">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="D176" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E176" t="s">
         <v>9</v>
@@ -6864,16 +6879,16 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177">
-        <v>23330051920240</v>
+        <v>23330051920215</v>
       </c>
       <c r="B177" t="s">
         <v>137</v>
       </c>
       <c r="C177" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="D177" t="s">
-        <v>275</v>
+        <v>412</v>
       </c>
       <c r="E177" t="s">
         <v>9</v>
@@ -6887,16 +6902,16 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178">
-        <v>23330051920244</v>
+        <v>23330051920216</v>
       </c>
       <c r="B178" t="s">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="C178" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D178" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E178" t="s">
         <v>9</v>
@@ -6910,16 +6925,16 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179">
-        <v>23330051920333</v>
+        <v>23330051920240</v>
       </c>
       <c r="B179" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="C179" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="D179" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E179" t="s">
         <v>9</v>
@@ -6933,16 +6948,16 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180">
-        <v>23330051920252</v>
+        <v>23330051920244</v>
       </c>
       <c r="B180" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="C180" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D180" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E180" t="s">
         <v>9</v>
@@ -6956,16 +6971,16 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181">
-        <v>23330051920239</v>
+        <v>23330051920333</v>
       </c>
       <c r="B181" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C181" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="D181" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E181" t="s">
         <v>9</v>
@@ -6979,16 +6994,16 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182">
-        <v>23330051920328</v>
+        <v>23330051920252</v>
       </c>
       <c r="B182" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C182" t="s">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="D182" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E182" t="s">
         <v>9</v>
@@ -7002,16 +7017,16 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183">
-        <v>23330051920256</v>
+        <v>23330051920239</v>
       </c>
       <c r="B183" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="C183" t="s">
-        <v>223</v>
+        <v>87</v>
       </c>
       <c r="D183" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E183" t="s">
         <v>9</v>
@@ -7025,16 +7040,16 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184">
-        <v>23330051920257</v>
+        <v>23330051920328</v>
       </c>
       <c r="B184" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="C184" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="D184" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E184" t="s">
         <v>9</v>
@@ -7048,16 +7063,16 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185">
-        <v>23330051920207</v>
+        <v>23330051920256</v>
       </c>
       <c r="B185" t="s">
-        <v>141</v>
+        <v>47</v>
       </c>
       <c r="C185" t="s">
-        <v>33</v>
+        <v>225</v>
       </c>
       <c r="D185" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E185" t="s">
         <v>9</v>
@@ -7071,16 +7086,16 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186">
-        <v>23330051920270</v>
+        <v>23330051920257</v>
       </c>
       <c r="B186" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C186" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D186" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="E186" t="s">
         <v>9</v>
@@ -7094,16 +7109,16 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187">
-        <v>23330051920276</v>
+        <v>23330051920207</v>
       </c>
       <c r="B187" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="C187" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="D187" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E187" t="s">
         <v>9</v>
@@ -7117,16 +7132,16 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188">
-        <v>23330051920277</v>
+        <v>23330051920270</v>
       </c>
       <c r="B188" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="C188" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="D188" t="s">
-        <v>420</v>
+        <v>328</v>
       </c>
       <c r="E188" t="s">
         <v>9</v>
@@ -7140,16 +7155,16 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189">
-        <v>23330051920279</v>
+        <v>23330051920276</v>
       </c>
       <c r="B189" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="C189" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D189" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E189" t="s">
         <v>9</v>
@@ -7163,22 +7178,22 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190">
-        <v>23330051920287</v>
+        <v>23330051920277</v>
       </c>
       <c r="B190" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="C190" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="D190" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E190" t="s">
         <v>9</v>
       </c>
       <c r="F190" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -7186,22 +7201,22 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191">
-        <v>23330051920288</v>
+        <v>23330051920279</v>
       </c>
       <c r="B191" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C191" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="D191" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E191" t="s">
         <v>9</v>
       </c>
       <c r="F191" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G191">
         <v>1</v>
@@ -7209,16 +7224,16 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192">
-        <v>23330051920290</v>
+        <v>23330051920319</v>
       </c>
       <c r="B192" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C192" t="s">
-        <v>225</v>
+        <v>124</v>
       </c>
       <c r="D192" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E192" t="s">
         <v>9</v>
@@ -7232,16 +7247,16 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193">
-        <v>23330051920300</v>
+        <v>23330051920287</v>
       </c>
       <c r="B193" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C193" t="s">
-        <v>226</v>
+        <v>72</v>
       </c>
       <c r="D193" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E193" t="s">
         <v>9</v>
@@ -7255,16 +7270,16 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>23330051920302</v>
+        <v>23330051920288</v>
       </c>
       <c r="B194" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="C194" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="D194" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E194" t="s">
         <v>9</v>
@@ -7278,16 +7293,16 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>23330051920304</v>
+        <v>23330051920289</v>
       </c>
       <c r="B195" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="C195" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D195" t="s">
-        <v>306</v>
+        <v>428</v>
       </c>
       <c r="E195" t="s">
         <v>9</v>
@@ -7301,22 +7316,22 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>23330051920029</v>
+        <v>23330051920290</v>
       </c>
       <c r="B196" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="C196" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
       <c r="D196" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E196" t="s">
         <v>9</v>
       </c>
       <c r="F196" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G196">
         <v>1</v>
@@ -7324,22 +7339,22 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>23330051920031</v>
+        <v>23330051920300</v>
       </c>
       <c r="B197" t="s">
         <v>147</v>
       </c>
       <c r="C197" t="s">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="D197" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E197" t="s">
         <v>9</v>
       </c>
       <c r="F197" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G197">
         <v>1</v>
@@ -7347,22 +7362,22 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>23330051920030</v>
+        <v>23330051920302</v>
       </c>
       <c r="B198" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="C198" t="s">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="D198" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E198" t="s">
         <v>9</v>
       </c>
       <c r="F198" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G198">
         <v>1</v>
@@ -7370,22 +7385,22 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>22330051920007</v>
+        <v>23330051920304</v>
       </c>
       <c r="B199" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="C199" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="D199" t="s">
-        <v>402</v>
+        <v>310</v>
       </c>
       <c r="E199" t="s">
         <v>9</v>
       </c>
       <c r="F199" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G199">
         <v>1</v>
@@ -7393,16 +7408,16 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>23330051920033</v>
+        <v>23330051920029</v>
       </c>
       <c r="B200" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="C200" t="s">
-        <v>229</v>
+        <v>33</v>
       </c>
       <c r="D200" t="s">
-        <v>376</v>
+        <v>432</v>
       </c>
       <c r="E200" t="s">
         <v>9</v>
@@ -7416,16 +7431,16 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>23330051920034</v>
+        <v>23330051920031</v>
       </c>
       <c r="B201" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="C201" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="D201" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E201" t="s">
         <v>9</v>
@@ -7439,16 +7454,16 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202">
-        <v>23330051920232</v>
+        <v>23330051920030</v>
       </c>
       <c r="B202" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C202" t="s">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="D202" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="E202" t="s">
         <v>9</v>
@@ -7462,16 +7477,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203">
-        <v>23330051920035</v>
+        <v>23330051920033</v>
       </c>
       <c r="B203" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="C203" t="s">
-        <v>126</v>
+        <v>231</v>
       </c>
       <c r="D203" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="E203" t="s">
         <v>9</v>
@@ -7485,16 +7500,16 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204">
-        <v>23330051920032</v>
+        <v>23330051920034</v>
       </c>
       <c r="B204" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="C204" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D204" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E204" t="s">
         <v>9</v>
@@ -7508,16 +7523,16 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205">
-        <v>23330051920039</v>
+        <v>23330051920232</v>
       </c>
       <c r="B205" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="C205" t="s">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="D205" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="E205" t="s">
         <v>9</v>
@@ -7531,16 +7546,16 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206">
-        <v>23330051920040</v>
+        <v>23330051920035</v>
       </c>
       <c r="B206" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="C206" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="D206" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E206" t="s">
         <v>9</v>
@@ -7554,16 +7569,16 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207">
-        <v>23330051920041</v>
+        <v>23330051920032</v>
       </c>
       <c r="B207" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C207" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="D207" t="s">
-        <v>298</v>
+        <v>437</v>
       </c>
       <c r="E207" t="s">
         <v>9</v>
@@ -7577,16 +7592,16 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208">
-        <v>23330051920042</v>
+        <v>23330051920039</v>
       </c>
       <c r="B208" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="C208" t="s">
-        <v>50</v>
+        <v>232</v>
       </c>
       <c r="D208" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E208" t="s">
         <v>9</v>
@@ -7600,16 +7615,16 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209">
-        <v>23330051920044</v>
+        <v>23330051920040</v>
       </c>
       <c r="B209" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="C209" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="D209" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E209" t="s">
         <v>9</v>
@@ -7623,16 +7638,16 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210">
-        <v>23330051920209</v>
+        <v>23330051920041</v>
       </c>
       <c r="B210" t="s">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="C210" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D210" t="s">
-        <v>437</v>
+        <v>302</v>
       </c>
       <c r="E210" t="s">
         <v>9</v>
@@ -7646,16 +7661,16 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211">
-        <v>23330051920210</v>
+        <v>23330051920042</v>
       </c>
       <c r="B211" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C211" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="D211" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E211" t="s">
         <v>9</v>
@@ -7669,16 +7684,16 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212">
-        <v>23330051920046</v>
+        <v>23330051920044</v>
       </c>
       <c r="B212" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C212" t="s">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="D212" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E212" t="s">
         <v>9</v>
@@ -7692,22 +7707,22 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213">
-        <v>23330051920116</v>
+        <v>23330051920209</v>
       </c>
       <c r="B213" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C213" t="s">
-        <v>60</v>
+        <v>234</v>
       </c>
       <c r="D213" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E213" t="s">
         <v>9</v>
       </c>
       <c r="F213" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G213">
         <v>1</v>
@@ -7715,22 +7730,22 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>23330051920117</v>
+        <v>23330051920210</v>
       </c>
       <c r="B214" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C214" t="s">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="D214" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E214" t="s">
         <v>9</v>
       </c>
       <c r="F214" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G214">
         <v>1</v>
@@ -7738,22 +7753,22 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215">
-        <v>23330051920118</v>
+        <v>23330051920046</v>
       </c>
       <c r="B215" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C215" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="D215" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E215" t="s">
         <v>9</v>
       </c>
       <c r="F215" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G215">
         <v>1</v>
@@ -7761,16 +7776,16 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216">
-        <v>23330061460223</v>
+        <v>23330051920116</v>
       </c>
       <c r="B216" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C216" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D216" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E216" t="s">
         <v>9</v>
@@ -7784,16 +7799,16 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217">
-        <v>23330051920119</v>
+        <v>23330051920117</v>
       </c>
       <c r="B217" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C217" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D217" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E217" t="s">
         <v>9</v>
@@ -7807,16 +7822,16 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218">
-        <v>23330051920120</v>
+        <v>23330051920118</v>
       </c>
       <c r="B218" t="s">
-        <v>65</v>
+        <v>159</v>
       </c>
       <c r="C218" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="D218" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E218" t="s">
         <v>9</v>
@@ -7830,16 +7845,16 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219">
-        <v>23330051920121</v>
+        <v>23330061460223</v>
       </c>
       <c r="B219" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C219" t="s">
-        <v>236</v>
+        <v>31</v>
       </c>
       <c r="D219" t="s">
-        <v>276</v>
+        <v>447</v>
       </c>
       <c r="E219" t="s">
         <v>9</v>
@@ -7853,16 +7868,16 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220">
-        <v>23330051920124</v>
+        <v>23330051920119</v>
       </c>
       <c r="B220" t="s">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="C220" t="s">
         <v>237</v>
       </c>
       <c r="D220" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E220" t="s">
         <v>9</v>
@@ -7876,16 +7891,16 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221">
-        <v>23330051920125</v>
+        <v>23330051920120</v>
       </c>
       <c r="B221" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C221" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="D221" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E221" t="s">
         <v>9</v>
@@ -7899,16 +7914,16 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222">
-        <v>23330051920126</v>
+        <v>23330051920121</v>
       </c>
       <c r="B222" t="s">
         <v>162</v>
       </c>
       <c r="C222" t="s">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="D222" t="s">
-        <v>447</v>
+        <v>277</v>
       </c>
       <c r="E222" t="s">
         <v>9</v>
@@ -7922,16 +7937,16 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223">
-        <v>23330051920127</v>
+        <v>23330051920124</v>
       </c>
       <c r="B223" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C223" t="s">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="D223" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E223" t="s">
         <v>9</v>
@@ -7945,16 +7960,16 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224">
-        <v>23330051920128</v>
+        <v>23330051920125</v>
       </c>
       <c r="B224" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C224" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="D224" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E224" t="s">
         <v>9</v>
@@ -7968,16 +7983,16 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225">
-        <v>23330051920129</v>
+        <v>23330051920126</v>
       </c>
       <c r="B225" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="C225" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D225" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E225" t="s">
         <v>9</v>
@@ -7991,16 +8006,16 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226">
-        <v>23330051920130</v>
+        <v>23330051920127</v>
       </c>
       <c r="B226" t="s">
         <v>43</v>
       </c>
       <c r="C226" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="D226" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E226" t="s">
         <v>9</v>
@@ -8014,16 +8029,16 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227">
-        <v>23330051920133</v>
+        <v>23330051920128</v>
       </c>
       <c r="B227" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="C227" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D227" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E227" t="s">
         <v>9</v>
@@ -8037,16 +8052,16 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228">
-        <v>23330051920134</v>
+        <v>23330051920129</v>
       </c>
       <c r="B228" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C228" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D228" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E228" t="s">
         <v>9</v>
@@ -8060,16 +8075,16 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229">
-        <v>23330051920135</v>
+        <v>23330051920130</v>
       </c>
       <c r="B229" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C229" t="s">
-        <v>186</v>
+        <v>240</v>
       </c>
       <c r="D229" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E229" t="s">
         <v>9</v>
@@ -8083,16 +8098,16 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230">
-        <v>23330051920137</v>
+        <v>23330051920133</v>
       </c>
       <c r="B230" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C230" t="s">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="D230" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E230" t="s">
         <v>9</v>
@@ -8106,16 +8121,16 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231">
-        <v>23330051920122</v>
+        <v>23330051920134</v>
       </c>
       <c r="B231" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="C231" t="s">
-        <v>185</v>
+        <v>43</v>
       </c>
       <c r="D231" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E231" t="s">
         <v>9</v>
@@ -8129,16 +8144,16 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232">
-        <v>23330051920140</v>
+        <v>23330051920135</v>
       </c>
       <c r="B232" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="C232" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
       <c r="D232" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E232" t="s">
         <v>9</v>
@@ -8152,16 +8167,16 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233">
-        <v>23330051920139</v>
+        <v>23330051920137</v>
       </c>
       <c r="B233" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="C233" t="s">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="D233" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E233" t="s">
         <v>9</v>
@@ -8175,16 +8190,16 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234">
-        <v>23330051920138</v>
+        <v>23330051920122</v>
       </c>
       <c r="B234" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="C234" t="s">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="D234" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E234" t="s">
         <v>9</v>
@@ -8198,16 +8213,16 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235">
-        <v>23330051920255</v>
+        <v>23330051920140</v>
       </c>
       <c r="B235" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="C235" t="s">
-        <v>241</v>
+        <v>95</v>
       </c>
       <c r="D235" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E235" t="s">
         <v>9</v>
@@ -8221,16 +8236,16 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236">
-        <v>23330051920141</v>
+        <v>23330051920139</v>
       </c>
       <c r="B236" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C236" t="s">
-        <v>242</v>
+        <v>108</v>
       </c>
       <c r="D236" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E236" t="s">
         <v>9</v>
@@ -8244,16 +8259,16 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237">
-        <v>23330051920315</v>
+        <v>23330051920138</v>
       </c>
       <c r="B237" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="C237" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D237" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E237" t="s">
         <v>9</v>
@@ -8267,16 +8282,16 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238">
-        <v>23330051920142</v>
+        <v>23330051920255</v>
       </c>
       <c r="B238" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="C238" t="s">
-        <v>75</v>
+        <v>243</v>
       </c>
       <c r="D238" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E238" t="s">
         <v>9</v>
@@ -8290,16 +8305,16 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239">
-        <v>23330051920143</v>
+        <v>23330051920141</v>
       </c>
       <c r="B239" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C239" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D239" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E239" t="s">
         <v>9</v>
@@ -8313,16 +8328,16 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240">
-        <v>23330051920146</v>
+        <v>23330051920315</v>
       </c>
       <c r="B240" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C240" t="s">
-        <v>33</v>
+        <v>245</v>
       </c>
       <c r="D240" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E240" t="s">
         <v>9</v>
@@ -8336,16 +8351,16 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241">
-        <v>23330051920147</v>
+        <v>23330051920142</v>
       </c>
       <c r="B241" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="C241" t="s">
-        <v>244</v>
+        <v>77</v>
       </c>
       <c r="D241" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E241" t="s">
         <v>9</v>
@@ -8359,16 +8374,16 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242">
-        <v>23330051920346</v>
+        <v>23330051920143</v>
       </c>
       <c r="B242" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="C242" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="D242" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E242" t="s">
         <v>9</v>
@@ -8382,16 +8397,16 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243">
-        <v>23330051920148</v>
+        <v>23330051920146</v>
       </c>
       <c r="B243" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="C243" t="s">
         <v>33</v>
       </c>
       <c r="D243" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E243" t="s">
         <v>9</v>
@@ -8405,16 +8420,16 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244">
-        <v>23330051920149</v>
+        <v>23330051920147</v>
       </c>
       <c r="B244" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C244" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D244" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E244" t="s">
         <v>9</v>
@@ -8428,16 +8443,16 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245">
-        <v>23330051920150</v>
+        <v>23330051920346</v>
       </c>
       <c r="B245" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="C245" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="D245" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E245" t="s">
         <v>9</v>
@@ -8446,6 +8461,75 @@
         <v>16</v>
       </c>
       <c r="G245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246">
+        <v>23330051920148</v>
+      </c>
+      <c r="B246" t="s">
+        <v>167</v>
+      </c>
+      <c r="C246" t="s">
+        <v>33</v>
+      </c>
+      <c r="D246" t="s">
+        <v>473</v>
+      </c>
+      <c r="E246" t="s">
+        <v>9</v>
+      </c>
+      <c r="F246" t="s">
+        <v>16</v>
+      </c>
+      <c r="G246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247">
+        <v>23330051920149</v>
+      </c>
+      <c r="B247" t="s">
+        <v>168</v>
+      </c>
+      <c r="C247" t="s">
+        <v>247</v>
+      </c>
+      <c r="D247" t="s">
+        <v>474</v>
+      </c>
+      <c r="E247" t="s">
+        <v>9</v>
+      </c>
+      <c r="F247" t="s">
+        <v>16</v>
+      </c>
+      <c r="G247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248">
+        <v>23330051920150</v>
+      </c>
+      <c r="B248" t="s">
+        <v>32</v>
+      </c>
+      <c r="C248" t="s">
+        <v>54</v>
+      </c>
+      <c r="D248" t="s">
+        <v>475</v>
+      </c>
+      <c r="E248" t="s">
+        <v>9</v>
+      </c>
+      <c r="F248" t="s">
+        <v>16</v>
+      </c>
+      <c r="G248">
         <v>1</v>
       </c>
     </row>
